--- a/data_extactor/batch_10_fa/batch_0017_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0017_fa.xlsx
@@ -503,32 +503,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>APLAC | ATD protocol | AVEVA InTouch HMI | Ada | Advanced boolean expression language ABEL | Altera hardware description language AHDL | Apache Subversion SVN | Autodesk AutoCAD | Autodesk AutoCAD Civil 3D | Autodesk Revit | نرم‌افزار جابجایی خودکار مواد | نرم‌افزار مدل‌سازی پیش‌بینی در دسترس بودن | Bash | Bentley MicroStation | C | C# | C++ | Cadence Allegro Design Entry Capture and Capture CIS | Cadence Encounter Test | نرم‌افزار طراحی تراشه | نرم‌افزار شبیه‌سازی مدار | نرم‌افزار طراحی و ترسیم به کمک کامپیوتر CADD | نرم‌افزار طراحی و ترسیم به کمک کامپیوتر CADD | Dassault Systemes CATIA | Dassault Systemes SolidWorks | نرم‌افزار عیب‌یابی | نرم‌افزار ردیابی نقص | نرم‌افزار ویرایش نمودار زمان‌بندی دیجیتال | سیستم الزامات پویا و شیءگرا DOORS | نرم‌افزار ESRI ArcGIS | ETAP | Eclipse IDE | نرم‌افزار تحلیل الکترومغناطیسی | نرم‌افزار اتوماسیون طراحی الکترونیکی EDA | ماشین‌حساب مهندسی الکترونیک | نرم‌افزار تست سیستم‌های تعبیه‌شده | نرم‌افزار تجزیه و تحلیل حالت‌های خرابی و اثرات آن FMEA | نرم‌افزار تجزیه و تحلیل حالت‌های خرابی، اثرات و بحرانی بودن آن FMECA | نرم‌افزار تجزیه و تحلیل گزارش خرابی و اقدامات اصلاحی FRACAS | نرم‌افزار مدل‌سازی خطا | نرم‌افزار تحلیل درخت خطا FTA | نرم‌افزار طراحی آرایه درگاه قابل برنامه‌ریزی فیلد FPGA | نرم‌افزار حوزه زمان تفاضل محدود FDTD | نرم‌افزار روش المان محدود FEM | نرم‌افزار برنامه‌ریزی چیدمان طبقات | نرم‌افزار تایید عملکردی | زبان توصیف سخت‌افزار HDL | Hewlett-Packard HP Semiconductor Parameter Analyzer | IBM Notes | نرم‌افزار محیط توسعه یکپارچه IDE | Isograph Markov | JHDL | Keysight Technologies Advanced Design System | نرم‌افزار هزینه چرخه عمر | Linux | نرم‌افزار سنتز منطقی | MAGIC | MathWorks Simulink | نرم‌افزار محاسبه ماتریس | نرم‌افزار میانگین زمان بین خرابی‌ها MBTF | نرم‌افزار میانگین زمان تا خرابی MTTF | نرم‌افزار Mentor Graphics | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft OneNote | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic Scripting Edition VBScript | Microsoft Visual Basic for Applications VBA | Microsoft Visual Studio | Microsoft Windows | Microsoft Windows Server | Microsoft Word | نرم‌افزار شبیه‌سازی مدار مایکروویو | Minitab | National Instruments LabVIEW | نرم‌افزار بهینه‌سازی | OrCAD Capture | Oracle E-Business Suite Financials | Oracle Primavera Enterprise Project Portfolio Management | PTC Creo Parametric | نرم‌افزار Perforce Helix | Perl | نرم‌افزار طراحی فیزیکی | نرم‌افزار تحلیل توان | Powersim PSIM | نرم‌افزار طراحی فیبر مدار چاپی | نرم‌افزار تولید کد کنترل‌کننده منطقی قابل برنامه‌ریزی PLC | نرم‌افزار کنترل‌کننده منطقی قابل برنامه‌ریزی PLC | Python | نرم‌افزار نمونه‌سازی سریع | ReliaSoft Weibull++ 6 | نرم‌افزار تحلیل قابلیت اطمینان | نرم‌افزار مدیریت الزامات | نرم‌افزار SAP | SKM Systems Analysis Power Tools | نرم‌افزار ورود طراحی شماتیک | Shell script | Siemens ModelSim | نرم‌افزار شبیه‌سازی یکپارچگی سیگنال | برنامه شبیه‌سازی با تاکید بر مدارهای مجتمع SPICE | SmugMug Flickr | Sun Microsystems Java | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | Synopsys Design Compiler | Synopsys PrimeTime | برنامه‌های تحلیل سیستم برای ارزیابی قابلیت اطمینان یکپارچه کاربردی نرم‌افزار SAPHIRE | Tektronix EZ-TEST | نرم‌افزار اتوماسیون تست | The MathWorks MATLAB | نرم‌افزار تحلیل زمان و حرکت | UNIX | زبان مدل‌سازی یکپارچه UML | Verilog | زبان توصیف سخت‌افزار مدار مجتمع با سرعت بسیار بالا VHSIC VHDL | X.25 Protocol | Zuken E3.schematic</t>
+          <t>APLAC | ATD protocol | AVEVA InTouch HMI | Ada | Advanced boolean expression language ABEL | Altera hardware description language AHDL | Apache Subversion SVN | Autodesk AutoCAD | Autodesk AutoCAD Civil 3D | Autodesk Revit | نرم‌افزار جابجایی خودکار مواد | نرم‌افزار مدل‌سازی پیش‌بینی در دسترس بودن | Bash | Bentley MicroStation | C | C# | C++ | Cadence Allegro Design Entry Capture and Capture CIS | Cadence Encounter Test | نرم‌افزار طراحی تراشه | نرم‌افزار شبیه‌سازی مدار | نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | Dassault Systemes CATIA | Dassault Systemes SolidWorks | نرم‌افزار عیب‌یابی | نرم‌افزار ردیابی نقص | نرم‌افزار ویرایش نمودار زمان‌بندی دیجیتال | سیستم الزامات پویا و شیءگرا DOORS | نرم‌افزار ESRI ArcGIS | ETAP | Eclipse IDE | نرم‌افزار تحلیل الکترومغناطیسی | نرم‌افزار اتوماسیون طراحی الکترونیکی EDA | ماشین‌حساب مهندسی الکترونیک | نرم‌افزار تست سیستم‌های تعبیه‌شده | نرم‌افزار تجزیه و تحلیل حالت‌های خرابی و اثرات آن FMEA | نرم‌افزار تجزیه و تحلیل حالت‌های خرابی، اثرات و بحرانی بودن آن FMECA | نرم‌افزار تجزیه و تحلیل گزارش خرابی و اقدامات اصلاحی FRACAS | نرم‌افزار مدل‌سازی خطا | نرم‌افزار تحلیل درخت خطا FTA | نرم‌افزار طراحی آرایه درگاه قابل برنامه‌ریزی فیلد FPGA | نرم‌افزار حوزه زمان تفاضل محدود FDTD | نرم‌افزار روش المان محدود FEM | نرم‌افزار برنامه‌ریزی چیدمان طبقات | نرم‌افزار تایید عملکردی | زبان توصیف سخت‌افزار HDL | Hewlett-Packard HP Semiconductor Parameter Analyzer | IBM Notes | نرم‌افزار محیط توسعه یکپارچه IDE | Isograph Markov | JHDL | Keysight Technologies Advanced Design System | نرم‌افزار هزینه چرخه عمر | Linux | نرم‌افزار سنتز منطق | MAGIC | MathWorks Simulink | نرم‌افزار محاسبه ماتریس | نرم‌افزار میانگین زمان بین خرابی‌ها MBTF | نرم‌افزار میانگین زمان تا خرابی MTTF | نرم‌افزار Mentor Graphics | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft OneNote | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic Scripting Edition VBScript | Microsoft Visual Basic for Applications VBA | Microsoft Visual Studio | Microsoft Windows | Microsoft Windows Server | Microsoft Word | نرم‌افزار شبیه‌سازی مدار مایکروویو | Minitab | National Instruments LabVIEW | نرم‌افزار بهینه‌سازی | OrCAD Capture | Oracle E-Business Suite Financials | Oracle Primavera Enterprise Project Portfolio Management | PTC Creo Parametric | نرم‌افزار Perforce Helix | Perl | نرم‌افزار طراحی فیزیکی | نرم‌افزار تحلیل توان | Powersim PSIM | نرم‌افزار طراحی فیبر مدار چاپی | نرم‌افزار تولید کد کنترل‌کننده منطقی قابل برنامه‌ریزی PLC | نرم‌افزار کنترل‌کننده منطقی قابل برنامه‌ریزی PLC | Python | نرم‌افزار نمونه‌سازی سریع | ReliaSoft Weibull++ 6 | نرم‌افزار تحلیل قابلیت اطمینان | نرم‌افزار مدیریت الزامات | نرم‌افزار SAP | ابزارهای قدرت تحلیل سیستم‌های SKM | نرم‌افزار ورود طراحی شماتیک | Shell script | Siemens ModelSim | نرم‌افزار شبیه‌سازی یکپارچگی سیگنال | برنامه شبیه‌سازی با تاکید بر مدارهای مجتمع SPICE | SmugMug Flickr | Sun Microsystems Java | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | Synopsys Design Compiler | Synopsys PrimeTime | برنامه‌های تحلیل سیستم برای ارزیابی قابلیت اطمینان یکپارچه SAPHIRE | Tektronix EZ-TEST | نرم‌افزار تست خودکار | The MathWorks MATLAB | نرم‌افزار تحلیل زمان و حرکت | UNIX | زبان مدل‌سازی یکپارچه UML | Verilog | زبان توصیف سخت‌افزار مدار مجتمع با سرعت بسیار بالا VHSIC VHDL | X.25 Protocol | Zuken E3.schematic</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>نگارش | تفکر انتقادی | درک مطلب | گوش دادن فعال | سخن گفتن | یادگیری فعال | نظارت | ریاضیات | استراتژی‌های یادگیری | علوم تجربی</t>
+          <t>نگارش | تفکر انتقادی | درک مطلب | گوش دادن فعال | سخن گفتن | یادگیری فعال | نظارت | ریاضیات | راهبردهای یادگیری | علوم</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | کامپیوتر و الکترونیک | طراحی | زبان انگلیسی | ریاضیات | فیزیک | تولید و فرآوری | مکانیک | امنیت و ایمنی عمومی | خدمات مشتریان و پرسنل</t>
+          <t>مهندسی و فناوری | رایانه و الکترونیک | طراحی | زبان انگلیسی | ریاضیات | فیزیک | تولید و فرآوری | مکانیک | ایمنی و امنیت عمومی | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک کتبی | بیان کتبی | درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی به اطلاعات | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | تشخیص گفتار | استدلال ریاضی | سهولت در کار با اعداد | روان بودن ایده‌ها | اصالت | وضوح گفتار | توجه انتخابی | تجسم فضایی | سرعت ادراکی | انعطاف‌پذیری بستار | بینایی دور</t>
+          <t>درک کتبی | بیان کتبی | درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | تشخیص گفتار | استدلال ریاضی | توانایی عددی | روانی ایده‌ها | اصالت | وضوح گفتار | توجه انتخابی | تجسم | سرعت ادراکی | انعطاف‌پذیری بستار | بینایی دور</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و در قالب تیم‌ها | محیط‌های داخلی، دارای کنترل دما | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | آزادی در تصمیم‌گیری | ارتباط با دیگران | کار با گروه یا تیم کاری یا مشارکت در آن | دفعات تصمیم‌گیری | صرف زمان به صورت نشسته | تاثیر تصمیمات بر همکاران یا نتایج شرکت | فشار زمانی | اهمیت تکرار وظایف یکسان | پیامدهای کاری و نتایج سایر کارکنان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | آزادی در تصمیم‌گیری | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | فراوانی تصمیم‌گیری | صرف زمان برای نشستن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فشار زمانی | اهمیت تکرار وظایف یکسان | پیامدهای کاری و نتایج سایر کارکنان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>تکنولوژیست‌ها و تکنسین‌های مهندسی هوافضا و عملیات | مهندسان خودرو | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | تکنولوژیست‌ها و تکنسین‌های مهندسی برق و الکترونیک | مونتاژکنندگان تجهیزات الکتریکی و الکترونیکی | نقشه کشان برق و الکترونیک | نصاب‌ها و تعمیرکاران برق و الکترونیک، تجهیزات حمل و نقل | تعمیرکاران برق و الکترونیک، تجهیزات تجاری و صنعتی | تعمیرکاران برق و الکترونیک، نیروگاه، پست برق و رله | مهندسان الکترونیک، به جز کامپیوتر | تکنولوژیست‌ها و تکنسین‌های مهندسی صنایع | مهندسان صنایع | مهندسان تولید | تکنولوژیست‌ها و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | مهندسان میکروسیستم‌ها | توزیع‌کنندگان و دیسپچرهای برق | تکنسین‌های رباتیک | مهندسان سیستم‌های انرژی خورشیدی</t>
+          <t>تکنسین‌ها و کارشناسان مهندسی و عملیات هوافضا | مهندسان خودرو | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | مونتاژکنندگان تجهیزات الکتریکی و الکترونیکی | نقشه‌کشان برق و الکترونیک | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات حمل و نقل | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، نیروگاه‌ها، پست‌های برق و رله‌ها | مهندسان الکترونیک، به جز کامپیوتر | تکنسین‌ها و کارشناسان مهندسی صنایع | مهندسان صنایع | مهندسان تولید | تکنسین‌ها و کارشناسان مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | مهندسان میکروسیستم | توزیع‌کنندگان و دیسپچرهای برق | تکنسین‌های رباتیک | مهندسان سیستم‌های انرژی خورشیدی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -560,32 +560,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Agile Product Lifecyle Management PLM | Ansoft Simplorer | Apache Subversion SVN | Autodesk AutoCAD | C | C++ | Cadence PSpice | Canu | Dassault Systemes CATIA | Dassault Systemes SolidWorks | نرم‌افزار ESRI ArcGIS | Embarcadero Delphi | زبان نشانه‌گذاری گسترش‌پذیر XML | نرم‌افزار طراحی آرایه درگاه قابل برنامه‌ریزی فیلد FPGA | مترجم فرمول FORTRAN | نرم‌افزار گرافیکی | Hewlett-Packard HP OpenVMS | IBM Lotus Notes | Linux | Magellan Firmware | MathWorks Simulink | Mathsoft Mathcad | McCabe Software TRUEchange | Mentor Graphics PADS | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Visual Basic.NET | Microsoft Visual C# .NET | Microsoft Word | National Instruments LabVIEW | OrCAD Capture | Oracle Database | Oracle Java | Python | Rabbit Semiconductor Dynamic C | نرم‌افزار سیستم‌عامل زمان واقعی RTOS | زبان پرس‌وجوی ساختاریافته SQL | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | Synopsys Saber | SystemVerilog | The MathWorks MATLAB | نرم‌افزار طراحی سه بعدی به کمک کامپیوتر CAD | Trimble SketchUp Pro | نرم‌افزار طراحی دو بعدی به کمک کامپیوتر CAD | UNIX | Verilog | نرم‌افزار شبیه‌سازی زبان توصیف سخت‌افزار مدار مجتمع با سرعت بسیار بالا VHSIC VHDL | زبان توصیف سخت‌افزار مدار مجتمع با سرعت بسیار بالا VHSIC VHDL | Visual Numerics PV-WAVE | نرم‌افزار مرورگر وب | Xilinx Integrated Software Environment ISE</t>
+          <t>Agile Product Lifecyle Management PLM | Ansoft Simplorer | Apache Subversion SVN | Autodesk AutoCAD | C | C++ | Cadence PSpice | Canu | Dassault Systemes CATIA | Dassault Systemes SolidWorks | نرم‌افزار ESRI ArcGIS | Embarcadero Delphi | زبان نشانه‌گذاری توسعه‌پذیر XML | نرم‌افزار طراحی آرایه درگاه قابل برنامه‌ریزی فیلد FPGA | Formula translation/translator FORTRAN | نرم‌افزار گرافیکی | Hewlett-Packard HP OpenVMS | IBM Lotus Notes | Linux | Magellan Firmware | MathWorks Simulink | Mathsoft Mathcad | McCabe Software TRUEchange | Mentor Graphics PADS | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Visual Basic.NET | Microsoft Visual C# .NET | Microsoft Word | National Instruments LabVIEW | OrCAD Capture | Oracle Database | Oracle Java | Python | Rabbit Semiconductor Dynamic C | نرم‌افزار سیستم‌عامل بلادرنگ RTOS | زبان پرس‌وجوی ساختاریافته SQL | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | Synopsys Saber | SystemVerilog | The MathWorks MATLAB | نرم‌افزار طراحی سه بعدی به کمک کامپیوتر CAD | Trimble SketchUp Pro | نرم‌افزار طراحی دو بعدی به کمک کامپیوتر CAD | UNIX | Verilog | نرم‌افزار شبیه‌سازی زبان توصیف سخت‌افزار VHSIC با سرعت بسیار بالا VHDL | زبان توصیف سخت‌افزار مدار مجتمع با سرعت بسیار بالا VHSIC VHDL | Visual Numerics PV-WAVE | نرم‌افزار مرورگر وب | Xilinx Integrated Software Environment ISE</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | سخن گفتن | گوش دادن فعال | نگارش | ریاضیات | نظارت | یادگیری فعال | استراتژی‌های یادگیری | علوم تجربی</t>
+          <t>درک مطلب | تفکر انتقادی | سخن گفتن | گوش دادن فعال | نگارش | ریاضیات | نظارت | یادگیری فعال | راهبردهای یادگیری | علوم</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | کامپیوتر و الکترونیک | طراحی | ریاضیات | زبان انگلیسی | مکانیک | فیزیک | آموزش و پرورش</t>
+          <t>مهندسی و فناوری | رایانه و الکترونیک | طراحی | ریاضیات | زبان انگلیسی | مکانیک | فیزیک | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>بیان شفاهی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی به اطلاعات | بینایی نزدیک | درک شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال ریاضی | روان بودن ایده‌ها | انعطاف‌پذیری دسته‌بندی | اصالت | تجسم فضایی | سهولت در کار با اعداد | تشخیص گفتار | انعطاف‌پذیری بستار | وضوح گفتار | زبردستی انگشتان | ثبات بازو-دست | سرعت ادراکی | سرعت بستار</t>
+          <t>بیان شفاهی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | بینایی نزدیک | درک شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال ریاضی | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | اصالت | تجسم | توانایی عددی | تشخیص گفتار | انعطاف‌پذیری بستار | وضوح گفتار | مهارت انگشتان | ثبات دست و بازو | سرعت ادراکی | سرعت بستار</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ایمیل | آزادی در تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و در قالب تیم‌ها | محیط‌های داخلی، دارای کنترل دما | کار با گروه یا تیم کاری یا مشارکت در آن | صرف زمان به صورت نشسته | اهمیت دقیق یا درست بودن | تعیین وظایف، اولویت‌ها و اهداف | ارتباط با دیگران | مکالمات تلفنی</t>
+          <t>ایمیل | آزادی در تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای نشستن | اهمیت دقیق یا درست بودن | تعیین وظایف، اولویت‌ها و اهداف | ارتباط با دیگران | مکالمات تلفنی</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>تکنولوژیست‌ها و تکنسین‌های مهندسی هوافضا و عملیات | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | مهندسان سخت‌افزار کامپیوتر | مهندسان برق | تکنولوژیست‌ها و تکنسین‌های مهندسی برق و الکترونیک | مونتاژکنندگان تجهیزات الکتریکی و الکترونیکی | نقشه کشان برق و الکترونیک | تعمیرکاران برق و الکترونیک، تجهیزات تجاری و صنعتی | تعمیرکاران برق و الکترونیک، نیروگاه، پست برق و رله | تکنولوژیست‌ها و تکنسین‌های الکترومکانیک و مکاترونیک | مونتاژکنندگان تجهیزات الکترومکانیکی | مهندسان صنایع | تکنولوژیست‌ها و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | مهندسان میکروسیستم‌ها | مهندسان فوتونیک | متخصصان دستگاه‌های شناسایی با فرکانس رادیویی | مهندسان رباتیک | تکنسین‌های رباتیک</t>
+          <t>تکنسین‌ها و کارشناسان مهندسی و عملیات هوافضا | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | مهندسان سخت‌افزار کامپیوتر | مهندسان برق | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | مونتاژکنندگان تجهیزات الکتریکی و الکترونیکی | نقشه‌کشان برق و الکترونیک | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، نیروگاه‌ها، پست‌های برق و رله‌ها | تکنسین‌ها و کارشناسان الکترومکانیک و مکاترونیک | مونتاژکاران تجهیزات الکترومکانیکی | مهندسان صنایع | تکنسین‌ها و کارشناسان مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | مهندسان میکروسیستم | مهندسان فوتونیک | متخصصان دستگاه‌های شناسایی با فرکانس رادیویی | مهندسان رباتیک | تکنسین‌های رباتیک</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ANSYS simulation software | Abbott | C | C# | C++ | CppUnit | Cygwin | Dassault Systemes SolidWorks | نرم‌افزار درایور دستگاه | پروتکل پیکربندی پویای میزبان DHCP | نرم‌افزار ESRI ArcGIS | زبان نشانه‌گذاری گسترش‌پذیر XML | نرم‌افزار طراحی آرایه درگاه قابل برنامه‌ریزی فیلد FPGA | FitNesse | Forsk Atoll | چارچوب تست یکپارچه FIT | IBM Notes | JUnit | Linux | Magellan Firmware | MapInfo Professional | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | Microsoft SQL Server Compact | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic Scripting Edition VBScript | Microsoft Visual Basic.NET | Microsoft Visual Basic.NET Compact Framework CF | Microsoft Visual Studio | Microsoft Windows Mobile | NUnit | National Instruments LabVIEW | Oracle Java | Perl | Python | Robot Framework | Ruby | نرم‌افزار SAP | Selenium | نرم‌افزار پروتکل آسان مدیریت شبکه SNMP | زبان پرس‌وجوی ساختاریافته SQL | The MathWorks MATLAB | UNIX | زبان مدل‌سازی یکپارچه UML | Verilog | Watir | نرم‌افزار مرورگر وب | Xilinx Integrated Software Environment ISE</t>
+          <t>نرم‌افزار شبیه‌سازی ANSYS | Abbott | C | C# | C++ | CppUnit | Cygwin | Dassault Systemes SolidWorks | نرم‌افزار درایور دستگاه | پروتکل پیکربندی پویای میزبان DHCP | نرم‌افزار ESRI ArcGIS | زبان نشانه‌گذاری توسعه‌پذیر XML | نرم‌افزار طراحی آرایه درگاه قابل برنامه‌ریزی فیلد FPGA | FitNesse | Forsk Atoll | چارچوب تست یکپارچه FIT | IBM Notes | JUnit | Linux | Magellan Firmware | MapInfo Professional | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | Microsoft SQL Server Compact | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic Scripting Edition VBScript | Microsoft Visual Basic.NET | Microsoft Visual Basic.NET Compact Framework CF | Microsoft Visual Studio | Microsoft Windows Mobile | NUnit | National Instruments LabVIEW | Oracle Java | Perl | Python | Robot Framework | Ruby | نرم‌افزار SAP | Selenium | نرم‌افزار پروتکل آسان مدیریت شبکه SNMP | زبان پرس‌وجوی ساختاریافته SQL | The MathWorks MATLAB | UNIX | زبان مدل‌سازی یکپارچه UML | Verilog | Watir | نرم‌افزار مرورگر وب | نرم‌افزار شبکه گسترده WAN</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -627,22 +627,22 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>کامپیوتر و الکترونیک | مهندسی و فناوری | زبان انگلیسی | طراحی | خدمات مشتریان و پرسنل | آموزش و پرورش | ریاضیات | مدیریت و سازماندهی | مخابرات | تولید و فرآوری | فروش و بازاریابی</t>
+          <t>رایانه و الکترونیک | مهندسی و فناوری | زبان انگلیسی | طراحی | خدمات مشتری و شخصی | آموزش و پرورش | ریاضیات | مدیریت و اداره | مخابرات | تولید و فرآوری | فروش و بازاریابی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>استدلالی قیاسی | درک شفاهی | حساسیت به مسئله | درک کتبی | استدلال استقرایی | ترتیب‌دهی به اطلاعات | بینایی نزدیک | بیان شفاهی | تشخیص گفتار | وضوح گفتار | بیان کتبی | روان بودن ایده‌ها | انعطاف‌پذیری دسته‌بندی | اصالت</t>
+          <t>استدلال قیاسی | درک شفاهی | حساسیت به مسئله | درک کتبی | استدلال استقرایی | ترتیب‌دهی اطلاعات | بینایی نزدیک | بیان شفاهی | تشخیص گفتار | وضوح گفتار | بیان کتبی | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | اصالت</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و در قالب تیم‌ها | محیط‌های داخلی، دارای کنترل دما | کار با گروه یا تیم کاری یا مشارکت در آن | ارتباط با دیگران | آزادی در تصمیم‌گیری | اهمیت دقیق یا درست بودن | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | فشار زمانی | صرف زمان به صورت نشسته | دفعات تصمیم‌گیری | برخورد با مشتریان خارجی یا عموم مردم | پیامدهای کاری و نتایج سایر کارکنان</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | آزادی در تصمیم‌گیری | اهمیت دقیق یا درست بودن | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فشار زمانی | صرف زمان برای نشستن | فراوانی تصمیم‌گیری | تعامل با مشتریان خارجی یا عموم مردم | پیامدهای کاری و نتایج سایر کارکنان</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>تکنولوژیست‌ها و تکنسین‌های مهندسی هوافضا و عملیات | تکنسین‌های پخش برنامه | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | مهندسان سخت‌افزار کامپیوتر | معماران شبکه کامپیوتری | مهندسان/معماران سیستم‌های کامپیوتری | مهندسان برق | تکنولوژیست‌ها و تکنسین‌های مهندسی برق و الکترونیک | تعمیرکاران برق و الکترونیک، تجهیزات تجاری و صنعتی | تکنولوژیست‌ها و تکنسین‌های الکترومکانیک و مکاترونیک | مهندسان الکترونیک، به جز کامپیوتر | مهندسان مکاترونیک | مهندسان میکروسیستم‌ها | مهندسان فوتونیک | تکنسین‌های فوتونیک | نصاب‌ها و تعمیرکاران تجهیزات رادیویی، سلولی و دکل | مهندسان رباتیک | تکنسین‌های رباتیک | توسعه‌دهندگان نرم‌افزار | متخصصان مهندسی مخابرات</t>
+          <t>تکنسین‌ها و کارشناسان مهندسی و عملیات هوافضا | تکنسین‌های پخش | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | مهندسان سخت‌افزار کامپیوتر | معماران شبکه کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | مهندسان برق | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | تکنسین‌ها و کارشناسان الکترومکانیک و مکاترونیک | مهندسان الکترونیک، به جز کامپیوتر | مهندسان مکاترونیک | مهندسان میکروسیستم | مهندسان فوتونیک | تکنسین‌های فوتونیک | نصابان و تعمیرکاران تجهیزات رادیویی، سلولی و دکل | مهندسان رباتیک | تکنسین‌های رباتیک | توسعه‌دهندگان نرم‌افزار | متخصصان مهندسی مخابرات</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,32 +674,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ANSYS simulation software | نرم‌افزار مدل‌سازی انتشار هوا | Autodesk AutoCAD | Autodesk AutoCAD Civil 3D | Bentley MicroStation | برنامه‌های نرم‌افزاری کسب‌وکار | C++ | نرم‌افزار طراحی و ترسیم به کمک کامپیوتر CADD | نرم‌افزار مدیریت انتشار مداوم | DHI Water and Environment MIKE SHE | نرم‌افزار ESRI ArcGIS | ESRI ArcView | نرم‌افزار ارزیابی ریسک اکولوژیکی | Eko | نرم‌افزار مستندسازی بهداشت و ایمنی محیط زیست | نرم‌افزار روش المان محدود FEM | مترجم فرمول FORTRAN | نرم‌افزار تشخیص نشت انتشار فرار | نرم‌افزار مدل انتشار گاز | سیستم‌های سیستم اطلاعات جغرافیایی GIS | نرم‌افزار تحلیل طراحی ژئومکانیکی GDA | نرم‌افزار مدیریت گازهای گلخانه‌ای | HEC-RAS | نرم‌افزار مدیریت مواد خطرناک HMS | نرم‌افزار برنامه شبیه‌سازی هیدرولوژیکی فرترن HSPF | نرم‌افزار تحلیل تصویر | Insightful S-PLUS | نرم‌افزار مدل‌سازی بهینه‌سازی سیستم‌های LINDO | Maplesoft Maple | نرم‌افزار برگه اطلاعات ایمنی مواد MSDS | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Project | Microsoft Word | نرم‌افزار نقشه‌برداری نفت | نرم‌افزار فتوگرامتری | Python | نرم‌افزار مدیریت انطباق با مقررات | RockWare MODFLOW | Rockwell Automation Arena | SAS | نرم‌افزار شبیه‌سازی | مکان‌یابی و نقشه‌برداری همزمان SLAM | نرم‌افزار مدیریت پاکسازی سایت | SofTech CADRA | نرم‌افزار مدل‌سازی رواناب آب‌های سطحی | The MathWorks MATLAB | نرم‌افزار WAM | نرم‌افزار مدیریت پسماند | نرم‌افزار مدل‌سازی جریان آب | نرم‌افزار مدل‌سازی جریان باد | XP Software XPSWMM</t>
+          <t>نرم‌افزار شبیه‌سازی ANSYS | نرم‌افزار مدل‌سازی انتشار هوا | Autodesk AutoCAD | Autodesk AutoCAD Civil 3D | Bentley MicroStation | برنامه‌های نرم‌افزاری تجاری | C++ | نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | نرم‌افزار مدیریت انتشار مداوم | DHI Water and Environment MIKE SHE | نرم‌افزار ESRI ArcGIS | ESRI ArcView | نرم‌افزار ارزیابی ریسک اکولوژیکی | Eko | نرم‌افزار مستندسازی بهداشت و ایمنی محیط زیست | نرم‌افزار روش المان محدود FEM | Formula translation/translator FORTRAN | نرم‌افزار تشخیص نشت انتشار فرار | نرم‌افزار مدل انتشار گاز | سیستم‌های سیستم اطلاعات جغرافیایی GIS | نرم‌افزار تحلیل طراحی ژئومکانیکی GDA | نرم‌افزار مدیریت گازهای گلخانه‌ای | HEC-RAS | نرم‌افزار مدیریت مواد خطرناک HMS | نرم‌افزار برنامه شبیه‌سازی هیدرولوژیکی فرترن HSPF | نرم‌افزار تحلیل تصویر | Insightful S-PLUS | نرم‌افزار مدل‌سازی بهینه‌سازی سیستم‌های LINDO | Maplesoft Maple | نرم‌افزار برگه اطلاعات ایمنی مواد MSDS | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Project | Microsoft Word | نرم‌افزار نقشه‌برداری نفت | نرم‌افزار فتوگرامتری | Python | نرم‌افزار مدیریت انطباق با مقررات | RockWare MODFLOW | Rockwell Automation Arena | SAS | نرم‌افزار شبیه‌سازی | مکان‌یابی و نقشه‌برداری همزمان SLAM | نرم‌افزار مدیریت پاکسازی سایت | SofTech CADRA | نرم‌افزار مدل‌سازی رواناب آب‌های سطحی | The MathWorks MATLAB | نرم‌افزار WAM | نرم‌افزار مدیریت پسماند | نرم‌افزار مدل‌سازی جریان آب | نرم‌افزار مدل‌سازی جریان باد | XP Software XPSWMM</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | نظارت | تفکر انتقادی | سخن گفتن | نگارش | درک مطلب | یادگیری فعال | ریاضیات | علوم تجربی | استراتژی‌های یادگیری</t>
+          <t>گوش دادن فعال | نظارت | تفکر انتقادی | سخن گفتن | نگارش | درک مطلب | یادگیری فعال | ریاضیات | علوم | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | طراحی | شیمی | ریاضیات | ساختمان و ساخت‌وساز | زبان انگلیسی | فیزیک | خدمات مشتریان و پرسنل | زیست‌شناسی | کامپیوتر و الکترونیک | حقوق و دولتی | مکانیک | مدیریت و سازماندهی | اقتصاد و حسابداری | امنیت و ایمنی عمومی | آموزش و پرورش</t>
+          <t>مهندسی و فناوری | طراحی | شیمی | ریاضیات | ساختمان و ساخت‌وساز | زبان انگلیسی | فیزیک | خدمات مشتری و شخصی | زیست‌شناسی | رایانه و الکترونیک | قانون و دولت | مکانیک | مدیریت و اداره | اقتصاد و حسابداری | ایمنی و امنیت عمومی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | روان بودن ایده‌ها | ترتیب‌دهی به اطلاعات | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | اصالت | سهولت در کار با اعداد | انعطاف‌پذیری بستار | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | تجسم فضایی | سرعت ادراکی | به خاطرسپاری</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | روانی ایده‌ها | ترتیب‌دهی اطلاعات | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | اصالت | توانایی عددی | انعطاف‌پذیری بستار | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | تجسم | سرعت ادراکی | حفظ کردن</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و در قالب تیم‌ها | کار با گروه یا تیم کاری یا مشارکت در آن | محیط‌های داخلی، دارای کنترل دما | اهمیت دقیق یا درست بودن | سلامت و ایمنی سایر کارکنان | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | برخورد با مشتریان خارجی یا عموم مردم | صرف زمان به صورت نشسته | تاثیر تصمیمات بر همکاران یا نتایج شرکت | فشار زمانی | آزادی در تصمیم‌گیری | نامه‌ها و یادداشت‌های مکتوب | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | پیامدهای کاری و نتایج سایر کارکنان | سطح رقابت</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل شرایط محیطی | اهمیت دقیق یا درست بودن | سلامت و ایمنی سایر کارکنان | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | تعامل با مشتریان خارجی یا عموم مردم | صرف زمان برای نشستن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فشار زمانی | آزادی در تصمیم‌گیری | نامه‌ها و یادداشت‌های کتبی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | پیامدهای کاری و نتایج سایر کارکنان | سطح رقابت</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>مهندسان کشاورزی | متخصصان توسعه مجدد و مدیران سایت براون‌فیلد | مهندسان شیمی | مهندسان عمران | دانشمندان حفاظت از منابع طبیعی | بازرسان انطباق محیط زیستی | تکنولوژیست‌ها و تکنسین‌های مهندسی محیط زیست | برنامه‌ریزان احیای محیط زیست | تکنسین‌های علوم و حفاظت محیط زیست، از جمله بهداشت | دانشمندان و متخصصان محیط زیست، از جمله بهداشت | مهندسان بهداشت و ایمنی، به جز مهندسان و بازرسان ایمنی معدن | تکنسین‌های هیدرولوژیکی | هیدرولوژیست‌ها | اکولوژیست‌های صنعتی | مهندسان هسته‌ای | متخصصان بهداشت و ایمنی شغلی | مهندسان نفت | متخصصان منابع آب | اپراتورهای سیستم و تصفیه‌خانه آب و فاضلاب | مهندسان آب و فاضلاب</t>
+          <t>مهندسان کشاورزی | متخصصان بازآفرینی زمین‌های قهوه‌ای و مدیران سایت | مهندسان شیمی | مهندسان عمران | دانشمندان حفاظت | بازرسان انطباق زیست‌محیطی | تکنسین‌ها و کارشناسان مهندسی محیط زیست | برنامه‌ریزان احیای محیط‌زیست | تکنسین‌های علم و حفاظت محیط زیست، شامل بهداشت | دانشمندان و متخصصان محیط زیست، شامل بهداشت | مهندسان بهداشت و ایمنی، به جز مهندسان و بازرسان ایمنی معدن | تکنسین‌های هیدرولوژی | آب‌شناسان | بوم‌شناسان صنعتی | مهندسان هسته‌ای | متخصصان بهداشت و ایمنی شغلی | مهندسان نفت | متخصصان منابع آب | اپراتورهای سیستم و تصفیه‌خانه آب و فاضلاب | مهندسان آب و فاضلاب</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -731,32 +731,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>پایگاه‌های داده آنتروپومتریک | Autodesk AutoCAD | نرم‌افزار مدل‌سازی پیش‌بینی در دسترس بودن | نرم‌افزار تصویربرداری بیومکانیکی | نرم‌افزار تحلیل ریسک آسیب بیومکانیکی | C++ | نرم‌افزار دینامیک سیالات محاسباتی CFD | Design Safety Engineering Designsafe | Eclipse IDE | نرم‌افزار اتوماسیون طراحی الکترونیکی EDA | نرم‌افزار پیش‌بینی مصرف انرژی EEP | نرم‌افزار تجزیه و تحلیل حالت‌های خرابی و اثرات آن FMEA | نرم‌افزار تجزیه و تحلیل حالت‌های خرابی، اثرات و بحرانی بودن آن FMECA | نرم‌افزار تحلیل حالت‌های خرابی | نرم‌افزار تجزیه و تحلیل گزارش خرابی و اقدامات اصلاحی FRACAS | نرم‌افزار تحلیل درخت خطا FTA | نرم‌افزار بازرسی و تست ایمنی آتش‌سوزی | نرم‌افزار تحلیل خطرات عملکردی | نرم‌افزار نقشه‌برداری زمین‌شناسی | نرم‌افزار تحلیل تنش ژئومکانیکی | نرم‌افزار ارزیابی خطر | نرم‌افزار ارتباطات خطر | نرم‌افزار آموزشی استاندارد عملیات پسماندهای خطرناک و واکنش اضطراری HAZWOPER | نرم‌افزار مدل‌سازی انسانی | نرم‌افزار ردیابی حوادث | نرم‌افزار ارزیابی مشاغل صنعتی | سیستم مدیریت بازرسی | Isograph FaultTree | Isograph Markov | Linux | نرم‌افزار پیش‌بینی قابلیت نگهداری | نرم‌افزار برگه اطلاعات ایمنی مواد MSDS | Mathsoft Mathcad | Microsoft Access | Microsoft Active Server Pages ASP | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SharePoint | Microsoft Visio | Microsoft Visual Basic | Microsoft Word | نرم‌افزار تحلیل ویدیویی چندرسانه‌ای | National Institute for Occupational Safety and Health LaModel | National Instruments LabVIEW | نرم‌افزار مدیریت مجوز | نرم‌افزار سم‌شناسی پیش‌بینی‌کننده | نرم‌افزار مستندسازی ایمنی محصول | Python | نرم‌افزار تحلیل کمی | نرم‌افزار مدیریت سوابق | ReliaSoft Weibull++ 6 | ReliaSoft XFMEA | نرم‌افزار تحلیل قابلیت اطمینان | نرم‌افزار نگهداری مبتنی بر قابلیت اطمینان RCM | نرم‌افزار اطلاعات قابلیت اطمینان | نرم‌افزار طراحی پشتیبانی سقف | نرم‌افزار تحلیل علت ریشه‌ای | نرم‌افزار SAP | نرم‌افزار سطح یکپارچگی ایمنی SIL | نرم‌افزار مدیریت ایمنی، بهداشت و محیط زیست | کتابخانه‌های نرم‌افزاری | نرم‌افزار پیش‌بینی قدرت استاتیک | نرم‌افزار نظرسنجی | The MathWorks MATLAB | نرم‌افزار تحلیل ارتعاش | نرم‌افزار شبیه‌ساز تعامل مجازی</t>
+          <t>پایگاه‌های داده آنتروپومتریک | Autodesk AutoCAD | نرم‌افزار مدل‌سازی پیش‌بینی در دسترس بودن | نرم‌افزار تصویربرداری بیومکانیکی | نرم‌افزار تحلیل ریسک آسیب بیومکانیکی | C++ | نرم‌افزار دینامیک سیالات محاسباتی CFD | Design Safety Engineering Designsafe | Eclipse IDE | نرم‌افزار اتوماسیون طراحی الکترونیکی EDA | نرم‌افزار پیش‌بینی مصرف انرژی EEP | نرم‌افزار تجزیه و تحلیل حالت‌های خرابی و اثرات آن FMEA | نرم‌افزار تجزیه و تحلیل حالت‌های خرابی، اثرات و بحرانی بودن آن FMECA | نرم‌افزار تحلیل حالت‌های خرابی | نرم‌افزار تجزیه و تحلیل گزارش خرابی و اقدامات اصلاحی FRACAS | نرم‌افزار تحلیل درخت خطا FTA | نرم‌افزار بازرسی و تست ایمنی آتش‌سوزی | نرم‌افزار تحلیل خطرات عملکردی | نرم‌افزار نقشه‌برداری زمین‌شناسی | نرم‌افزار تحلیل تنش ژئومکانیکی | نرم‌افزار ارزیابی خطر | نرم‌افزار ارتباطات خطر | نرم‌افزار آموزشی استاندارد عملیات پسماندهای خطرناک و واکنش اضطراری HAZWOPER | نرم‌افزار مدل‌سازی انسانی | نرم‌افزار ردیابی حوادث | نرم‌افزار ارزیابی مشاغل صنعتی | سیستم مدیریت بازرسی | Isograph FaultTree | Isograph Markov | Linux | نرم‌افزار پیش‌بینی قابلیت نگهداری | نرم‌افزار برگه اطلاعات ایمنی مواد MSDS | Mathsoft Mathcad | Microsoft Access | Microsoft Active Server Pages ASP | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SharePoint | Microsoft Visio | Microsoft Visual Basic | Microsoft Word | نرم‌افزار تحلیل ویدیویی چندرسانه‌ای | National Institute for Occupational Safety and Health LaModel | National Instruments LabVIEW | نرم‌افزار مدیریت مجوز | نرم‌افزار سم‌شناسی پیش‌بینی‌کننده | نرم‌افزار مستندسازی ایمنی محصول | Python | نرم‌افزار تحلیل کمی | نرم‌افزار مدیریت سوابق | ReliaSoft Weibull++ 6 | ReliaSoft XFMEA | نرم‌افزار تحلیل قابلیت اطمینان | نرم‌افزار نگهداری متمرکز بر قابلیت اطمینان RCM | نرم‌افزار اطلاعات قابلیت اطمینان | نرم‌افزار طراحی پشتیبانی سقف | نرم‌افزار تحلیل علت ریشه‌ای | نرم‌افزار SAP | نرم‌افزار سطح یکپارچگی ایمنی SIL | نرم‌افزار مدیریت ایمنی، بهداشت و محیط زیست | کتابخانه‌های نرم‌افزاری | نرم‌افزار پیش‌بینی قدرت استاتیک | نرم‌افزار نظرسنجی | The MathWorks MATLAB | نرم‌افزار تحلیل ارتعاش | نرم‌افزار شبیه‌ساز تعامل مجازی</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>درک مطلب | گوش دادن فعال | نگارش | تفکر انتقادی | سخن گفتن | نظارت | استراتژی‌های یادگیری | یادگیری فعال</t>
+          <t>درک مطلب | گوش دادن فعال | نگارش | تفکر انتقادی | سخن گفتن | نظارت | راهبردهای یادگیری | یادگیری فعال</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | مهندسی و فناوری | مدیریت و سازماندهی | امنیت و ایمنی عمومی | خدمات مشتریان و پرسنل | حقوق و دولتی | آموزش و پرورش | مکانیک | ریاضیات | شیمی | طراحی | تولید و فرآوری | اداری | فیزیک | ساختمان و ساخت‌وساز | روانشناسی | پرسنل و منابع انسانی | کامپیوتر و الکترونیک</t>
+          <t>زبان انگلیسی | مهندسی و فناوری | مدیریت و اداره | ایمنی و امنیت عمومی | خدمات مشتری و شخصی | قانون و دولت | آموزش و پرورش | مکانیک | ریاضیات | شیمی | طراحی | تولید و فرآوری | اداری | فیزیک | ساختمان و ساخت‌وساز | روان‌شناسی | پرسنل و منابع انسانی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>استدلال استقرایی | استدلال قیاسی | درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | بیان کتبی | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | روان بودن ایده‌ها | تشخیص گفتار | بینایی نزدیک | ترتیب‌دهی به اطلاعات | اصالت | بینایی دور | انعطاف‌پذیری بستار | توجه انتخابی | سرعت ادراکی | تمایز رنگ‌های بینایی</t>
+          <t>استدلال استقرایی | استدلال قیاسی | درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | بیان کتبی | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | تشخیص گفتار | بینایی نزدیک | ترتیب‌دهی اطلاعات | اصالت | بینایی دور | انعطاف‌پذیری بستار | توجه انتخابی | سرعت ادراکی | تشخیص رنگ بصری</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و در قالب تیم‌ها | مکالمات تلفنی | اهمیت دقیق یا درست بودن | ارتباط با دیگران | آزادی در تصمیم‌گیری | کار با گروه یا تیم کاری یا مشارکت در آن | تاثیر تصمیمات بر همکاران یا نتایج شرکت | سلامت و ایمنی سایر کارکنان | پوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | تعیین وظایف، اولویت‌ها و اهداف | محیط‌های داخلی، دارای کنترل دما | دفعات تصمیم‌گیری | فشار زمانی | نامه‌ها و یادداشت‌های مکتوب | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
+          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | اهمیت دقیق یا درست بودن | ارتباط با دیگران | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | تأثیر تصمیمات بر همکاران یا نتایج شرکت | سلامت و ایمنی سایر کارکنان | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | تعیین وظایف، اولویت‌ها و اهداف | محیط داخلی، دارای کنترل شرایط محیطی | فراوانی تصمیم‌گیری | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>بازرسان کشاورزی | بازرسان هوانوردی | مدیران انطباق | بازرسان ساختمان و سازه | بازرسان انطباق محیط زیستی | تکنولوژیست‌ها و تکنسین‌های مهندسی محیط زیست | مهندسان محیط زیست | تکنسین‌های علوم و حفاظت محیط زیست، از جمله بهداشت | دانشمندان و متخصصان محیط زیست، از جمله بهداشت | مهندسان پیشگیری و حفاظت از آتش‌سوزی | مهندسان عوامل انسانی و ارگونومیست‌ها | تکنولوژیست‌ها و تکنسین‌های مهندسی صنایع | مهندسان صنایع | متخصصان بهداشت و ایمنی شغلی | تکنسین‌های بهداشت و ایمنی شغلی | تست‌کنندگان نفوذ | مدیران سیستم‌های کنترل کیفیت | متخصصان مدیریت امنیت | بازرسان وسایل نقلیه، تجهیزات و سیستم‌های حمل و نقل، به جز هوانوردی | مهندسان اعتبارسنجی</t>
+          <t>بازرسان کشاورزی | بازرسان هوانوردی | مدیران انطباق | بازرسان ساختمان و ساخت‌وساز | بازرسان انطباق زیست‌محیطی | تکنسین‌ها و کارشناسان مهندسی محیط زیست | مهندسان محیط زیست | تکنسین‌های علم و حفاظت محیط زیست، شامل بهداشت | دانشمندان و متخصصان محیط زیست، شامل بهداشت | مهندسان پیشگیری و حفاظت از آتش‌سوزی | مهندسان عوامل انسانی و ارگونومیست‌ها | تکنسین‌ها و کارشناسان مهندسی صنایع | مهندسان صنایع | متخصصان بهداشت و ایمنی شغلی | تکنسین‌های بهداشت و ایمنی شغلی | کارشناسان آزمون نفوذ | مدیران سیستم‌های کنترل کیفیت | متخصصان مدیریت امنیت | بازرسان وسایل نقلیه، تجهیزات و سیستم‌های حمل‌ونقل، به جز هوانوردی | مهندسان اعتبارسنجی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -788,32 +788,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>A Large Outdoor Fire plume Trajectory model Flat Terrain ALOFT-FT | ANSYS simulation software | Analysis of Smoke Control Systems ASCOS | Atria smoke management engineering tools ASMET | Autodesk AutoCAD | Autodesk Revit | Available Safe Egress Time ASET | Bentley MicroStation | Berkeley Algorithm for Breaking Window Glass in a Compartment Fire BREAK1 | Building Research Establishment BRE Jasmine | CESARE Risk | Computational Dynamics STAR-CD | نرم‌افزار دینامیک سیالات محاسباتی CFD | Consolidated compartment fire model CCFM | Consolidated fire and smoke transport model CFAST | Crows Dynamics Simulex | نرم‌افزار جمع‌آوری داده | Detector Actuation Quasi Steady DETACT-QS | Egress Allsafe | Egress EVACS | نرم‌افزار تخلیه آسانسور ELVAC | نرم‌افزار مدل‌سازی تخلیه | نرم‌افزار مدل‌سازی منطقه آتش FIRECALC | نرم‌افزار روش المان محدود FEM | نرم‌افزار ابزارهای مهندسی حفاظت از آتش FPETool | نرم‌افزار حرارتی پاسخ آتش سازه‌ها FIRES-T | نرم‌افزار تکنیک شبیه‌سازی آتش FIRST | شبیه‌سازهای دینامیک آتش | Fluent FloWizard | نرم‌افزار مدل‌سازی انسانی | Interconsult Brann G-JET | JET | نرم‌افزار شبیه‌سازی گردابه‌های بزرگ LES | نرم‌افزار دریچه‌های فعال‌شده با پیوند LAVENT | نرم‌افزار تحلیل تحمل بار | نرم‌افزار میانگین زمان تا خرابی MTTF | نرم‌افزار طراحی مکانیک، برق و لوله‌کشی MEP | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Project | Microsoft Visio | Microsoft Windows | Microsoft Word | نرم‌افزار مدل‌سازی جریان شبکه | نرم‌افزار شبیه‌سازی آتش در محفظه‌ها SOFIE | نرم‌افزار مدل‌سازی منطقه</t>
+          <t>A Large Outdoor Fire plume Trajectory model Flat Terrain ALOFT-FT | نرم‌افزار شبیه‌سازی ANSYS | Analysis of Smoke Control Systems ASCOS | Atria smoke management engineering tools ASMET | Autodesk AutoCAD | Autodesk Revit | Available Safe Egress Time ASET | Bentley MicroStation | Berkeley Algorithm for Breaking Window Glass in a Compartment Fire BREAK1 | Building Research Establishment BRE Jasmine | CESARE Risk | Computational Dynamics STAR-CD | نرم‌افزار دینامیک سیالات محاسباتی CFD | Consolidated compartment fire model CCFM | Consolidated fire and smoke transport model CFAST | Crows Dynamics Simulex | نرم‌افزار جمع‌آوری داده | Detector Actuation Quasi Steady DETACT-QS | Egress Allsafe | Egress EVACS | نرم‌افزار تخلیه آسانسور ELVAC | نرم‌افزار مدل‌سازی تخلیه | نرم‌افزار مدل‌سازی منطقه آتش FIRECALC | نرم‌افزار روش المان محدود FEM | نرم‌افزار ابزارهای مهندسی حفاظت از آتش FPETool | نرم‌افزار حرارتی پاسخ آتش سازه‌ها FIRES-T | نرم‌افزار تکنیک شبیه‌سازی آتش FIRST | شبیه‌سازهای دینامیک آتش | Fluent FloWizard | نرم‌افزار مدل‌سازی انسانی | Interconsult Brann G-JET | JET | نرم‌افزار شبیه‌سازی گردابه‌های بزرگ LES | نرم‌افزار دریچه‌های فعال‌شده با پیوند LAVENT | نرم‌افزار تحلیل تحمل بار | نرم‌افزار میانگین زمان تا خرابی MTTF | نرم‌افزار طراحی مکانیک، برق و لوله‌کشی MEP | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Project | Microsoft Visio | Microsoft Windows | Microsoft Word | نرم‌افزار مدل‌سازی جریان شبکه | نرم‌افزار شبیه‌سازی آتش در محفظه‌ها SOFIE | نرم‌افزار مدل‌سازی منطقه</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | درک مطلب | گوش دادن فعال | نگارش | یادگیری فعال | علوم تجربی | ریاضیات | استراتژی‌های یادگیری | نظارت</t>
+          <t>تفکر انتقادی | سخن گفتن | درک مطلب | گوش دادن فعال | نگارش | یادگیری فعال | علوم | ریاضیات | راهبردهای یادگیری | نظارت</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | ساختمان و ساخت‌وساز | طراحی | امنیت و ایمنی عمومی | ریاضیات | زبان انگلیسی | فیزیک | شیمی | خدمات مشتریان و پرسنل | مکانیک | حقوق و دولتی | کامپیوتر و الکترونیک | آموزش و پرورش | مدیریت و سازماندهی</t>
+          <t>مهندسی و فناوری | ساختمان و ساخت‌وساز | طراحی | ایمنی و امنیت عمومی | ریاضیات | زبان انگلیسی | فیزیک | شیمی | خدمات مشتری و شخصی | مکانیک | قانون و دولت | رایانه و الکترونیک | آموزش و پرورش | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | وضوح گفتار | ترتیب‌دهی به اطلاعات | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | تشخیص گفتار | روان بودن ایده‌ها | بینایی دور | تجسم فضایی | اصالت | استدلال ریاضی | سرعت ادراکی | سهولت در کار با اعداد | تمایز رنگ‌های بینایی | سرعت بستار</t>
+          <t>حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | وضوح گفتار | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | تشخیص گفتار | روانی ایده‌ها | بینایی دور | تجسم | اصالت | استدلال ریاضی | سرعت ادراکی | توانایی عددی | تشخیص رنگ بصری | سرعت بستار</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و در قالب تیم‌ها | ارتباط با دیگران | محیط‌های داخلی، دارای کنترل دما | کار با گروه یا تیم کاری یا مشارکت در آن | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | نامه‌ها و یادداشت‌های مکتوب | اهمیت دقیق یا درست بودن | صرف زمان به صورت نشسته | برخورد با مشتریان خارجی یا عموم مردم | تاثیر تصمیمات بر همکاران یا نتایج شرکت | فشار زمانی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | محیط داخلی، دارای کنترل شرایط محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | نامه‌ها و یادداشت‌های کتبی | اهمیت دقیق یا درست بودن | صرف زمان برای نشستن | تعامل با مشتریان خارجی یا عموم مردم | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فشار زمانی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>تکنولوژیست‌ها و تکنسین‌های مهندسی عمران | مهندسان عمران | بازرسان ساختمان و سازه | مدیران مدیریت بحران | بازرسان انطباق محیط زیستی | تکنولوژیست‌ها و تکنسین‌های مهندسی محیط زیست | مهندسان محیط زیست | بازرسان و محققان آتش‌سوزی | آتش‌نشان‌ها | سرپرستان رده اول آتش‌نشانی و کارکنان پیشگیری | بازرسان آتش‌سوزی جنگل و متخصصان پیشگیری | بازرسان و محققان اموال دولتی | مهندسان بهداشت و ایمنی، به جز مهندسان و بازرسان ایمنی معدن | مهندسان هسته‌ای | متخصصان بهداشت و ایمنی شغلی | تکنسین‌های بهداشت و ایمنی شغلی | تست‌کنندگان نفوذ | متخصصان مدیریت امنیت | نصاب‌های سیستم‌های امنیتی و اعلام حریق | مهندسان آب و فاضلاب</t>
+          <t>تکنسین‌ها و کارشناسان مهندسی عمران | مهندسان عمران | بازرسان ساختمان و ساخت‌وساز | مدیران مدیریت بحران | بازرسان انطباق زیست‌محیطی | تکنسین‌ها و کارشناسان مهندسی محیط زیست | مهندسان محیط زیست | بازرسان و محققان آتش‌نشانی | آتش‌نشانان | سرپرستان خط اول آتش‌نشانی و پیشگیری | بازرسان و متخصصان پیشگیری از آتش‌سوزی جنگل | بازرسان و محققان اموال دولتی | مهندسان بهداشت و ایمنی، به جز مهندسان و بازرسان ایمنی معدن | مهندسان هسته‌ای | متخصصان بهداشت و ایمنی شغلی | تکنسین‌های بهداشت و ایمنی شغلی | کارشناسان آزمون نفوذ | متخصصان مدیریت امنیت | نصب‌کنندگان سیستم‌های دزدگیر و اعلام حریق | مهندسان آب و فاضلاب</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3D Static Strength Prediction Program 3DSSPP | A mathematical programming language AMPL | Allen Bradley PanelView | نرم‌افزار متعادل‌سازی خط مونتاژ | Autodesk AutoCAD | Automatic dynamic incremental nonlinear analysis ADINA | Bentley MicroStation | C++ | نرم‌افزار کنترل عددی کامپیوتری CNC | Dassault Systemes Abaqus | Dassault Systemes CATIA | Dassault Systemes SolidWorks | نرم‌افزار جمع‌آوری داده | Dataxiom StatMost | نرم‌افزار پشتیبانی تصمیم‌گیری | نرم‌افزار طراحی آزمایش‌ها DOE | نرم‌افزار شبیه‌سازی رویداد گسسته | ECHIP | EGS FeatureCAM | ETA Dynaform | نرم‌افزار برد بورد الکترونیکی | زبان نشانه‌گذاری گسترش‌پذیر XML | نرم‌افزار طراحی تاسیسات | نرم‌افزار برنامه‌ریزی تاسیسات | نرم‌افزار روش المان محدود FEM | GitHub | Hewlett Packard LoadRunner | Human machine interface HMI software | نرم‌افزار مدل‌سازی انسانی | IBM Notes | ILOG CPLEX | نرم‌افزار محیط توسعه یکپارچه IDE | International TechneGroup IGESworks | JUnit | Linux | نرم‌افزار برنامه‌نویسی منطقی | MAGMA MAGMASOFT | Main Injector Neutrino Oscillation Search MINOS software | Manhattan Associates PkMS Pickticket | Maplesoft Maple | نرم‌افزار برنامه‌ریزی نیازمندی‌های مواد MRP | Mathsoft Mathcad | Maya HTT I-DEAS | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | Microsoft SharePoint | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic Scripting Edition VBScript | Microsoft Visual Basic for Applications VBA | Microsoft Visual Studio | Microsoft Word | Minitab | نرم‌افزار چیدمان مدولار استانداردهای زمان از پیش تعیین شده MODAPTS | National Instruments LabVIEW | نرم‌افزار مدل‌سازی شبکه عصبی | NeuralWare | نرم‌افزار کنترل عددی | Nupro CastView | نرم‌افزار بهینه‌سازی | Oracle Retek | PMC KanbanSIM | PTC Creo Parametric | نرم‌افزار زمان‌بندی پرسنل | ProModel | نرم‌افزار مهندسی مجدد فرآیند | نرم‌افزار تحلیل جریان تولید | نرم‌افزار زمان‌بندی و برنامه‌ریزی تولید | Python | نرم‌افزار کنترل کیفیت | R | نرم‌افزار کنترل رباتیک | نرم‌افزار شبیه‌سازی رباتیک | Rockwell Automation Arena | Rockwell RSLogix | نرم‌افزار SAP | SAS | Shell script | Siemens UGS Jack | Statgraphics | نرم‌افزار آماری | Stratasys FDM MedModeler | زبان پرس‌وجوی ساختاریافته SQL | Sun Microsystems Java | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | نرم‌افزار برنامه‌ریزی ظرفیت زنجیره تامین | نرم‌افزار تحلیل وظایف | The MathWorks MATLAB | نرم‌افزار ترجمه شبیه‌سازی سه بعدی | نرم‌افزار تحلیل زمان و حرکت | UGS Solid Edge | UNIX Shell | نرم‌افزار طراحی رابط کاربری | Warehouse management system WMS | Windward Technologies GRG2 | Wolfram Research Mathematica | نرم‌افزار شبیه‌سازی سلول کاری | سیستم‌های مدیریت بازده</t>
+          <t>3D Static Strength Prediction Program 3DSSPP | A mathematical programming language AMPL | Allen Bradley PanelView | نرم‌افزار متعادل‌سازی خط مونتاژ | Autodesk AutoCAD | Automatic dynamic incremental nonlinear analysis ADINA | Bentley MicroStation | C++ | نرم‌افزار کنترل عددی کامپیوتری CNC | Dassault Systemes Abaqus | Dassault Systemes CATIA | Dassault Systemes SolidWorks | نرم‌افزار جمع‌آوری داده | Dataxiom StatMost | نرم‌افزار پشتیبانی تصمیم‌گیری | نرم‌افزار طراحی آزمایش‌ها DOE | نرم‌افزار شبیه‌سازی رویداد گسسته | ECHIP | EGS FeatureCAM | ETA Dynaform | نرم‌افزار برد بورد الکترونیکی | زبان نشانه‌گذاری توسعه‌پذیر XML | نرم‌افزار طراحی تاسیسات | نرم‌افزار برنامه‌ریزی تاسیسات | نرم‌افزار روش المان محدود FEM | GitHub | Hewlett Packard LoadRunner | نرم‌افزار رابط انسان و ماشین HMI | نرم‌افزار مدل‌سازی انسانی | IBM Notes | ILOG CPLEX | نرم‌افزار محیط توسعه یکپارچه IDE | International TechneGroup IGESworks | JUnit | Linux | نرم‌افزار برنامه‌نویسی منطقی | MAGMA MAGMASOFT | Main Injector Neutrino Oscillation Search MINOS software | Manhattan Associates PkMS Pickticket | Maplesoft Maple | نرم‌افزار برنامه‌ریزی نیازمندی‌های مواد MRP | Mathsoft Mathcad | Maya HTT I-DEAS | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | Microsoft SharePoint | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic Scripting Edition VBScript | Microsoft Visual Basic for Applications VBA | Microsoft Visual Studio | Microsoft Word | Minitab | نرم‌افزار چیدمان مدولار استانداردهای زمان از پیش تعیین شده MODAPTS | National Instruments LabVIEW | نرم‌افزار مدل‌سازی شبکه عصبی | NeuralWare | نرم‌افزار کنترل عددی | Nupro CastView | نرم‌افزار بهینه‌سازی | Oracle Retek | PMC KanbanSIM | PTC Creo Parametric | نرم‌افزار زمان‌بندی پرسنل | ProModel | نرم‌افزار مهندسی مجدد فرآیند | نرم‌افزار تحلیل جریان تولید | نرم‌افزار زمان‌بندی و برنامه‌ریزی تولید | Python | نرم‌افزار کنترل کیفیت | R | نرم‌افزار کنترل رباتیک | نرم‌افزار شبیه‌سازی رباتیک | Rockwell Automation Arena | Rockwell RSLogix | نرم‌افزار SAP | SAS | Shell script | Siemens UGS Jack | Statgraphics | نرم‌افزار آماری | Stratasys FDM MedModeler | زبان پرس‌وجوی ساختاریافته SQL | Sun Microsystems Java | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | نرم‌افزار برنامه‌ریزی ظرفیت زنجیره تامین | نرم‌افزار تحلیل وظایف | The MathWorks MATLAB | نرم‌افزار ترجمه شبیه‌سازی سه بعدی | نرم‌افزار تحلیل زمان و حرکت | UGS Solid Edge | UNIX Shell | نرم‌افزار طراحی رابط کاربری | سیستم مدیریت انبار WMS | Windward Technologies GRG2 | Wolfram Research Mathematica | نرم‌افزار شبیه‌سازی سلول کاری | سیستم‌های مدیریت بازده</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -855,22 +855,22 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | تولید و فرآوری | مکانیک | طراحی | زبان انگلیسی | ریاضیات | کامپیوتر و الکترونیک | مدیریت و سازماندهی | خدمات مشتریان و پرسنل | آموزش و پرورش | امنیت و ایمنی عمومی | فیزیک | اداری</t>
+          <t>مهندسی و فناوری | تولید و فرآوری | مکانیک | طراحی | زبان انگلیسی | ریاضیات | رایانه و الکترونیک | مدیریت و اداره | خدمات مشتری و شخصی | آموزش و پرورش | ایمنی و امنیت عمومی | فیزیک | اداری</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | درک شفاهی | درک کتبی | حساسیت به مسئله | بینایی نزدیک | ترتیب‌دهی به اطلاعات | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | روان بودن ایده‌ها | اصالت | تشخیص گفتار | وضوح گفتار | تجسم فضایی | سهولت در کار با اعداد | استدلال ریاضی | انعطاف‌پذیری بستار | بینایی دور</t>
+          <t>بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | درک شفاهی | درک کتبی | حساسیت به مسئله | بینایی نزدیک | ترتیب‌دهی اطلاعات | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | تشخیص گفتار | وضوح گفتار | تجسم | توانایی عددی | استدلال ریاضی | انعطاف‌پذیری بستار | بینایی دور</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و در قالب تیم‌ها | مکالمات تلفنی | کار با گروه یا تیم کاری یا مشارکت در آن | ارتباط با دیگران | محیط‌های داخلی، دارای کنترل دما | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | اهمیت دقیق یا درست بودن | پوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | برخورد با مشتریان خارجی یا عموم مردم | تاثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | دفعات تصمیم‌گیری | فشار زمانی | پیامدهای کاری و نتایج سایر کارکنان | نامه‌ها و یادداشت‌های مکتوب</t>
+          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | محیط داخلی، دارای کنترل شرایط محیطی | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | اهمیت دقیق یا درست بودن | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | تعامل با مشتریان خارجی یا عموم مردم | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فراوانی تصمیم‌گیری | فشار زمانی | پیامدهای کاری و نتایج سایر کارکنان | نامه‌ها و یادداشت‌های کتبی</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>تکنولوژیست‌ها و تکنسین‌های مهندسی هوافضا و عملیات | مدیران معماری و مهندسی | مهندسان خودرو | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | مهندسان برق | تکنولوژیست‌ها و تکنسین‌های مهندسی برق و الکترونیک | مهندسان الکترونیک، به جز کامپیوتر | مهندسان عوامل انسانی و ارگونومیست‌ها | تکنولوژیست‌ها و تکنسین‌های مهندسی صنایع | مدیران تولید صنعتی | مهندسان لجستیک | مهندسان تولید | مهندسان مواد | تکنولوژیست‌ها و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | متخصصان مدیریت پروژه | مدیران سیستم‌های کنترل کیفیت | مونتاژکنندگان تیم | مهندسان اعتبارسنجی</t>
+          <t>تکنسین‌ها و کارشناسان مهندسی و عملیات هوافضا | مدیران معماری و مهندسی | مهندسان خودرو | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | مهندسان برق | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | مهندسان الکترونیک، به جز کامپیوتر | مهندسان عوامل انسانی و ارگونومیست‌ها | تکنسین‌ها و کارشناسان مهندسی صنایع | مدیران تولید صنعتی | مهندسان لجستیک | مهندسان تولید | مهندسان مواد | تکنسین‌ها و کارشناسان مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | متخصصان مدیریت پروژه | مدیران سیستم‌های کنترل کیفیت | مونتاژکاران تیمی | مهندسان اعتبارسنجی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -902,32 +902,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>AEMC DataView | AJAX | Adobe Acrobat | نرم‌افزار Adobe Creative Cloud | Adobe Dreamweaver | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Altia Design | Apple Safari | Atlassian JIRA | Autodesk AutoCAD | Bit Debris Solutions Usability Activity Log | C++ | Cascading style sheets CSS | Dartfish ProSuite | Dassault Systemes CATIA | Dassault Systemes SolidWorks | Data Translation quickDAQ | نرم‌افزار عیب‌یابی | زبان نشانه‌گذاری ابرمتن پویا DHTML | زبان نشانه‌گذاری گسترش‌پذیر XML | نرم‌افزار طراحی رابط کاربری گرافیکی GUI | زبان نشانه‌گذاری ابرمتن HTML | IBM SPSS Statistics | JavaScript | JavaScript Object Notation JSON | Linux | Mangold INTERACT | Mangold LogSquare | Mangold Soundalyzer | MathWorks Simulink | Microsoft Excel | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Visio | Microsoft Visual Basic | Microsoft Word | Mozilla Firefox | National Instruments LabVIEW | Noldus Information Technology FaceReader | Noldus Information Technology The Observer XT | Noldus Information Technology uLog Pro | Oracle Java | Ovo Studios Ovo Logger | Python | R | نرم‌افزار تست رگرسیون | SAS | Seeing Machines faceLAB | نرم‌افزار شبیه‌سازی | نرم‌افزار آماری | TechSmith Camtasia | TechSmith Morae | The MathWorks MATLAB | Thought Technology BioGraph Infiniti | Triangle Research Collaborative Observational Coding System OCS Tools | نرم‌افزار تست کاربردپذیری | نرم‌افزار طراحی رابط کاربری | jQuery</t>
+          <t>AEMC DataView | AJAX | Adobe Acrobat | نرم‌افزار Adobe Creative Cloud | Adobe Dreamweaver | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Altia Design | Apple Safari | Atlassian JIRA | Autodesk AutoCAD | Bit Debris Solutions Usability Activity Log | C++ | برگه‌های سبک آبشاری CSS | Dartfish ProSuite | Dassault Systemes CATIA | Dassault Systemes SolidWorks | Data Translation quickDAQ | نرم‌افزار عیب‌یابی | زبان نشانه‌گذاری ابرمتن پویا DHTML | زبان نشانه‌گذاری توسعه‌پذیر XML | نرم‌افزار طراحی رابط کاربری گرافیکی GUI | زبان نشانه‌گذاری ابرمتن HTML | IBM SPSS Statistics | JavaScript | JavaScript Object Notation JSON | Linux | Mangold INTERACT | Mangold LogSquare | Mangold Soundalyzer | MathWorks Simulink | Microsoft Excel | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Visio | Microsoft Visual Basic | Microsoft Word | Mozilla Firefox | National Instruments LabVIEW | Noldus Information Technology FaceReader | Noldus Information Technology The Observer XT | Noldus Information Technology uLog Pro | Oracle Java | Ovo Studios Ovo Logger | Python | R | نرم‌افزار تست رگرسیون | SAS | Seeing Machines faceLAB | نرم‌افزار شبیه‌سازی | نرم‌افزار آماری | TechSmith Camtasia | TechSmith Morae | The MathWorks MATLAB | Thought Technology BioGraph Infiniti | Triangle Research Collaborative Observational Coding System OCS Tools | نرم‌افزار تست کاربردپذیری | نرم‌افزار طراحی رابط کاربری | jQuery</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | نگارش | گوش دادن فعال | درک مطلب | یادگیری فعال | نظارت | ریاضیات | استراتژی‌های یادگیری | علوم تجربی</t>
+          <t>تفکر انتقادی | سخن گفتن | نگارش | گوش دادن فعال | درک مطلب | یادگیری فعال | نظارت | ریاضیات | راهبردهای یادگیری | علوم</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>روانشناسی | زبان انگلیسی | طراحی | مهندسی و فناوری | آموزش و پرورش | ریاضیات | خدمات مشتریان و پرسنل | جامعه‌شناسی و انسان‌شناسی | تولید و فرآوری | کامپیوتر و الکترونیک | مدیریت و سازماندهی</t>
+          <t>روان‌شناسی | زبان انگلیسی | طراحی | مهندسی و فناوری | آموزش و پرورش | ریاضیات | خدمات مشتری و شخصی | جامعه‌شناسی و انسان‌شناسی | تولید و فرآوری | رایانه و الکترونیک | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی به اطلاعات | روان بودن ایده‌ها | انعطاف‌پذیری دسته‌بندی | اصالت | وضوح گفتار | استدلال ریاضی | بینایی نزدیک | تشخیص گفتار | سهولت در کار با اعداد | تجسم فضایی | بینایی دور | سرعت ادراکی | انعطاف‌پذیری بستار | سرعت بستار</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | اصالت | وضوح گفتار | استدلال ریاضی | بینایی نزدیک | تشخیص گفتار | توانایی عددی | تجسم | بینایی دور | سرعت ادراکی | انعطاف‌پذیری بستار | سرعت بستار</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | آزادی در تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و در قالب تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | محیط‌های داخلی، دارای کنترل دما | کار با گروه یا تیم کاری یا مشارکت در آن | ارتباط با دیگران | سلامت و ایمنی سایر کارکنان | اهمیت دقیق یا درست بودن | نامه‌ها و یادداشت‌های مکتوب | صرف زمان به صورت نشسته | فشار زمانی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
+          <t>ایمیل | مکالمات تلفنی | آزادی در تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | محیط داخلی، دارای کنترل شرایط محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | سلامت و ایمنی سایر کارکنان | اهمیت دقیق یا درست بودن | نامه‌ها و یادداشت‌های کتبی | صرف زمان برای نشستن | فشار زمانی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>زیست‌مهندسان و مهندسان پزشکی | مدیران داده‌های بالینی | دانشمندان تحقیقات کامپیوتر و اطلاعات | دانشمندان داده | تکنولوژیست‌ها و تکنسین‌های مهندسی برق و الکترونیک | متخصصان انفورماتیک سلامت | مهندسان بهداشت و ایمنی، به جز مهندسان و بازرسان ایمنی معدن | تکنولوژیست‌ها و تکنسین‌های مهندسی صنایع | مهندسان صنایع | مهندسان تولید | تکنولوژیست‌ها و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | تکنولوژیست‌ها و تکنسین‌های مهندسی نانو فناوری | متخصصان بهداشت و ایمنی شغلی | تکنسین‌های بهداشت و ایمنی شغلی | تست‌کنندگان نفوذ | مهندسان رباتیک | تحلیل‌گران و تست‌کنندگان تضمین کیفیت نرم‌افزار | مهندسان اعتبارسنجی</t>
+          <t>مهندسان زیستی و مهندسان زیست‌پزشکی | مدیران داده‌های بالینی | دانشمندان تحقیقات کامپیوتر و اطلاعات | دانشمندان داده | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | متخصصان انفورماتیک سلامت | مهندسان بهداشت و ایمنی، به جز مهندسان و بازرسان ایمنی معدن | تکنسین‌ها و کارشناسان مهندسی صنایع | مهندسان صنایع | مهندسان تولید | تکنسین‌ها و کارشناسان مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | تکنسین‌ها و کارشناسان مهندسی نانوتکنولوژی | متخصصان بهداشت و ایمنی شغلی | تکنسین‌های بهداشت و ایمنی شغلی | کارشناسان آزمون نفوذ | مهندسان رباتیک | تحلیل‌گران و تست‌کنندگان تضمین کیفیت نرم‌افزار | مهندسان اعتبارسنجی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -959,32 +959,32 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Amazon DynamoDB | Amazon Elastic Compute Cloud EC2 | Amazon Web Services AWS CloudFormation | نرم‌افزار Amazon Web Services AWS | نرم‌افزار Ansible | Apache Ant | Apache Cassandra | Apache Groovy | Apache HTTP Server | Apache Kafka | Apache Maven | Apache Solr | Apache Struts | Apache Subversion SVN | Apache Tomcat | Atlassian Bamboo | Atlassian JIRA | Bash | Bugzilla | C | C# | C++ | Cadence Incisive Enterprise Simulator | Cadence Incisive Enterprise Specman Elite Testbench | Chef | Dassault Systemes CATIA | Dassault Systemes SolidWorks | Django | Docker | EMC Documentum | Elasticsearch | نرم‌افزار ایمیل | زبان نشانه‌گذاری گسترش‌پذیر XML | GE Intelligent Platforms Proficy HMI/SCADA iFIX | Git | GitHub | Go | Grafana Labs Grafana Cloud | Hewlett Packard LoadRunner | Hewlett Packard QuickTest Professional | IBM Notes | IBM Rational ClearQuest | IBM Terraform | IndySoft Gage InSite Enterprise | JUnit | JavaScript | Jenkins CI | Kubernetes | سیستم مدیریت اطلاعات آزمایشگاهی LIMS | Linux | شبیه‌سازهای منطقی | Microsoft Access | نرم‌افزار Microsoft Azure | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Power Automate | Microsoft Power BI | نرم‌افزار Microsoft Power Platform | Microsoft PowerPoint | Microsoft PowerShell | Microsoft Project | Microsoft SQL Server | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Studio | Microsoft Windows | Microsoft Word | Minitab | MongoDB | MySQL | Nagios | National Instruments LabVIEW | NoSQL | Node.js | Oracle Java | PHP | PTC Creo Parametric | نرم‌افزار Perforce Helix | Perl | PostgreSQL | Prometheus | Puppet | Python | QUALCOMM eXtensible Diagnostic Monitor QxDM | R | Red Hat Enterprise Linux | Red Hat OpenShift | Red Hat WildFly | Ruby | Ruby on Rails | Scala | Selenium | Shell script | برنامه شبیه‌سازی با تاکید بر مدارهای مجتمع SPICE | نرم‌افزار شبیه‌سازی | Sparta Systems TrackWise | Splunk Enterprise | نرم‌افزار آماری | Structure query language SQL | Structured query language SQL | نرم‌افزار طراحی الکترونیک Synopsys | Teradata Database | The MathWorks MATLAB | UNIX | UNIX Shell | Ubuntu | Verilog | زبان توصیف سخت‌افزار مدار مجتمع با سرعت بسیار بالا VHSIC VHDL | نرم‌افزار شبکه خصوصی مجازی VPN | دیباگرهای هسته ویندوز | Wireshark</t>
+          <t>Amazon DynamoDB | Amazon Elastic Compute Cloud EC2 | Amazon Web Services AWS CloudFormation | نرم‌افزار Amazon Web Services AWS | نرم‌افزار Ansible | Apache Ant | Apache Cassandra | Apache Groovy | Apache HTTP Server | Apache Kafka | Apache Maven | Apache Solr | Apache Struts | Apache Subversion SVN | Apache Tomcat | Atlassian Bamboo | Atlassian JIRA | Bash | Bugzilla | C | C# | C++ | Cadence Incisive Enterprise Simulator | Cadence Incisive Enterprise Specman Elite Testbench | Chef | Dassault Systemes CATIA | Dassault Systemes SolidWorks | Django | Docker | EMC Documentum | Elasticsearch | نرم‌افزار ایمیل | زبان نشانه‌گذاری توسعه‌پذیر XML | GE Intelligent Platforms Proficy HMI/SCADA iFIX | Git | GitHub | Go | Grafana Labs Grafana Cloud | Hewlett Packard LoadRunner | Hewlett Packard QuickTest Professional | IBM Notes | IBM Rational ClearQuest | IBM Terraform | IndySoft Gage InSite Enterprise | JUnit | JavaScript | Jenkins CI | Kubernetes | سیستم مدیریت اطلاعات آزمایشگاهی LIMS | Linux | شبیه‌سازهای منطقی | Microsoft Access | نرم‌افزار Microsoft Azure | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Power Automate | Microsoft Power BI | نرم‌افزار Microsoft Power Platform | Microsoft PowerPoint | Microsoft PowerShell | Microsoft Project | Microsoft SQL Server | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Studio | Microsoft Windows | Microsoft Word | Minitab | MongoDB | MySQL | Nagios | National Instruments LabVIEW | NoSQL | Node.js | Oracle Java | PHP | PTC Creo Parametric | نرم‌افزار Perforce Helix | Perl | PostgreSQL | Prometheus | Puppet | Python | QUALCOMM eXtensible Diagnostic Monitor QxDM | R | Red Hat Enterprise Linux | Red Hat OpenShift | Red Hat WildFly | Ruby | Ruby on Rails | Scala | Selenium | Shell script | برنامه شبیه‌سازی با تاکید بر مدارهای مجتمع SPICE | نرم‌افزار شبیه‌سازی | Sparta Systems TrackWise | Splunk Enterprise | نرم‌افزار آماری | زبان پرس‌وجوی ساختاریافته SQL | زبان پرس‌وجوی ساختاریافته SQL | نرم‌افزار طراحی الکترونیک Synopsys | Teradata Database | The MathWorks MATLAB | UNIX | UNIX Shell | Ubuntu | Verilog | زبان توصیف سخت‌افزار مدار مجتمع با سرعت بسیار بالا VHSIC VHDL | نرم‌افزار شبکه خصوصی مجازی VPN | دیباگرهای هسته ویندوز | Wireshark</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>درک مطلب | سخن گفتن | تفکر انتقادی | نگارش | گوش دادن فعال | نظارت | علوم تجربی | یادگیری فعال | ریاضیات | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | سخن گفتن | تفکر انتقادی | نگارش | گوش دادن فعال | نظارت | علوم | یادگیری فعال | ریاضیات | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | تولید و فرآوری | زبان انگلیسی | خدمات مشتریان و پرسنل | ریاضیات | طراحی | مکانیک | آموزش و پرورش | کامپیوتر و الکترونیک | مدیریت و سازماندهی</t>
+          <t>مهندسی و فناوری | تولید و فرآوری | زبان انگلیسی | خدمات مشتری و شخصی | ریاضیات | طراحی | مکانیک | آموزش و پرورش | رایانه و الکترونیک | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک کتبی | بیان کتبی | استدلال قیاسی | درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال استقرایی | بینایی نزدیک | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی به اطلاعات | تشخیص گفتار | استدلال ریاضی | روان بودن ایده‌ها | سهولت در کار با اعداد | سرعت ادراکی | انعطاف‌پذیری بستار | توجه انتخابی | اصالت</t>
+          <t>درک کتبی | بیان کتبی | استدلال قیاسی | درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال استقرایی | بینایی نزدیک | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | تشخیص گفتار | استدلال ریاضی | روانی ایده‌ها | توانایی عددی | سرعت ادراکی | انعطاف‌پذیری بستار | توجه انتخابی | اصالت</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و در قالب تیم‌ها | اهمیت دقیق یا درست بودن | محیط‌های داخلی، دارای کنترل دما | کار با گروه یا تیم کاری یا مشارکت در آن | مکالمات تلفنی | آزادی در تصمیم‌گیری | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | فشار زمانی | صرف زمان به صورت نشسته | تاثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | اهمیت تکرار وظایف یکسان</t>
+          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | محیط داخلی، دارای کنترل شرایط محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | مکالمات تلفنی | آزادی در تصمیم‌گیری | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | فشار زمانی | صرف زمان برای نشستن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | اهمیت تکرار وظایف یکسان</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>تکنولوژیست‌ها و تکنسین‌های مهندسی هوافضا و عملیات | تکنسین‌های مهندسی خودرو | مهندسان خودرو | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | مهندسان برق | تکنولوژیست‌ها و تکنسین‌های مهندسی برق و الکترونیک | تعمیرکاران برق و الکترونیک، تجهیزات تجاری و صنعتی | مهندسان الکترونیک، به جز کامپیوتر | مهندسان عوامل انسانی و ارگونومیست‌ها | تکنولوژیست‌ها و تکنسین‌های مهندسی صنایع | مهندسان صنایع | مهندسان تولید | تکنولوژیست‌ها و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | تست‌کنندگان نفوذ | تحلیل‌گران کنترل کیفیت | مدیران سیستم‌های کنترل کیفیت | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و تست‌کنندگان تضمین کیفیت نرم‌افزار</t>
+          <t>تکنسین‌ها و کارشناسان مهندسی و عملیات هوافضا | تکنسین‌های مهندسی خودرو | مهندسان خودرو | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | مهندسان برق | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | مهندسان الکترونیک، به جز کامپیوتر | مهندسان عوامل انسانی و ارگونومیست‌ها | تکنسین‌ها و کارشناسان مهندسی صنایع | مهندسان صنایع | مهندسان تولید | تکنسین‌ها و کارشناسان مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | کارشناسان آزمون نفوذ | تحلیل‌گران کنترل کیفیت | مدیران سیستم‌های کنترل کیفیت | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و تست‌کنندگان تضمین کیفیت نرم‌افزار</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,27 +1021,27 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ریاضیات | درک مطلب | سخن گفتن | نظارت | گوش دادن فعال | نگارش | تفکر انتقادی | یادگیری فعال | استراتژی‌های یادگیری | علوم تجربی</t>
+          <t>ریاضیات | درک مطلب | سخن گفتن | نظارت | گوش دادن فعال | نگارش | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری | علوم</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | تولید و فرآوری | مکانیک | طراحی | ریاضیات | کامپیوتر و الکترونیک | زبان انگلیسی | فیزیک | مدیریت و سازماندهی | آموزش و پرورش</t>
+          <t>مهندسی و فناوری | تولید و فرآوری | مکانیک | طراحی | ریاضیات | رایانه و الکترونیک | زبان انگلیسی | فیزیک | مدیریت و اداره | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>انعطاف‌پذیری دسته‌بندی | تجسم فضایی | بینایی نزدیک | درک شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک کتبی | بیان شفاهی | ترتیب‌دهی به اطلاعات | استدلال ریاضی | سهولت در کار با اعداد | بیان کتبی | روان بودن ایده‌ها | اصالت | انعطاف‌پذیری بستار | تشخیص گفتار | بینایی دور | وضوح گفتار | توجه انتخابی | سرعت ادراکی | سرعت بستار</t>
+          <t>انعطاف‌پذیری دسته‌بندی | تجسم | بینایی نزدیک | درک شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک کتبی | بیان شفاهی | ترتیب‌دهی اطلاعات | استدلال ریاضی | توانایی عددی | بیان کتبی | روانی ایده‌ها | اصالت | انعطاف‌پذیری بستار | تشخیص گفتار | بینایی دور | وضوح گفتار | توجه انتخابی | سرعت ادراکی | سرعت بستار</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و در قالب تیم‌ها | مکالمات تلفنی | محیط‌های داخلی، دارای کنترل دما | کار با گروه یا تیم کاری یا مشارکت در آن | پوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | ارتباط با دیگران | اهمیت دقیق یا درست بودن | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | سلامت و ایمنی سایر کارکنان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | فشار زمانی | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند</t>
+          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | محیط داخلی، دارای کنترل شرایط محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | ارتباط با دیگران | اهمیت دقیق یا درست بودن | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | سلامت و ایمنی سایر کارکنان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فشار زمانی | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>تکنولوژیست‌ها و تکنسین‌های مهندسی هوافضا و عملیات | مهندسان خودرو | مهندسان شیمی | مهندسان برق | تکنولوژیست‌ها و تکنسین‌های مهندسی برق و الکترونیک | مهندسان الکترونیک، به جز کامپیوتر | مهندسان عوامل انسانی و ارگونومیست‌ها | تکنولوژیست‌ها و تکنسین‌های مهندسی صنایع | مهندسان صنایع | مدیران تولید صنعتی | مهندسان لجستیک | مهندسان مواد | دانشمندان مواد | تکنولوژیست‌ها و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | مهندسان میکروسیستم‌ها | تکنسین‌های رباتیک | مونتاژکنندگان تیم | مهندسان اعتبارسنجی</t>
+          <t>تکنسین‌ها و کارشناسان مهندسی و عملیات هوافضا | مهندسان خودرو | مهندسان شیمی | مهندسان برق | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | مهندسان الکترونیک، به جز کامپیوتر | مهندسان عوامل انسانی و ارگونومیست‌ها | تکنسین‌ها و کارشناسان مهندسی صنایع | مهندسان صنایع | مدیران تولید صنعتی | مهندسان لجستیک | مهندسان مواد | دانشمندان مواد | تکنسین‌ها و کارشناسان مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | مهندسان میکروسیستم | تکنسین‌های رباتیک | مونتاژکاران تیمی | مهندسان اعتبارسنجی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0017_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0017_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>نگارش | تفکر انتقادی | درک مطلب | شنیدن فعال | سخن گفتن | یادگیری فعال | نظارت | ریاضیات | استراتژی‌های یادگیری | علوم پایه</t>
+          <t>نگارش | تفکر انتقادی | درک مطلب | گوش دادن فعال | سخن گفتن | یادگیری فعال | نظارت | ریاضیات | راهبردهای یادگیری | علوم</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | رایانه و الکترونیک | طراحی | زبان انگلیسی | ریاضیات | فیزیک | تولید و فرآوری | مکانیک | ایمنی و امنیت عمومی | خدمات مشتریان و خدمات فردی</t>
+          <t>مهندسی و فناوری | رایانه و الکترونیک | طراحی | زبان انگلیسی | ریاضیات | فیزیک | تولید و فرآوری | مکانیک | ایمنی و امنیت عمومی | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک کتبی | بیان کتبی | درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | انعطاف‌پذیری در طبقه‌بندی | دید نزدیک | تشخیص گفتار | استدلال ریاضی | محاسبات عددی | روانی ایده‌ها | اصالت و ابتکار | وضوح گفتار | توجه انتخابی | تجسم فضایی | سرعت ادراک | انعطاف‌پذیری نتیجه‌گیری | دید دور</t>
+          <t>درک کتبی | بیان کتبی | درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | تشخیص گفتار | استدلال ریاضی | توانایی عددی | روانی ایده‌ها | اصالت | وضوح گفتار | توجه انتخابی | تجسم | سرعت ادراکی | انعطاف‌پذیری بستار | بینایی دور</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و کارشناسان فناوری مهندسی و عملیات هوافضا | مهندسان خودرو | تکنسین‌ها و کارشناسان فناوری کالیبراسیون | تکنسین‌ها و کارشناسان فناوری مهندسی برق و الکترونیک | مونتاژکاران تجهیزات برق و الکترونیک | نقشه‌کش‌های برق و الکترونیک | نصابان و تعمیرکاران برق و الکترونیک تجهیزات حمل‌ونقل | تعمیرکاران تجهیزات تجاری و صنعتی برق و الکترونیک | تعمیرکاران برق و الکترونیک نیروگاه، پست برق و رله | مهندسان الکترونیک، به‌جز کامپیوتر | تکنسین‌ها و کارشناسان فناوری مهندسی صنایع | مهندسان صنایع | مهندسان تولید و ساخت | تکنسین‌ها و کارشناسان فناوری مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | مهندسان میکروسیستم‌ها | توزیع‌کنندگان و دیسپچرهای برق | تکنسین‌های رباتیک | مهندسان سامانه‌های انرژی خورشیدی</t>
+          <t>کارشناسان و تکنسین‌های مهندسی و عملیات هوافضا | مهندسان خودرو | تکنسین‌ها و کارشناسان فنی کالیبراسیون | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | نقشه‌کشان برق و الکترونیک | نصاب و تعمیرکار تجهیزات الکتریکی و الکترونیکی وسایل نقلیه | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | تعمیرکار تجهیزات الکتریکی نیروگاه، پست برق و رله | مهندسان الکترونیک، به‌جز کامپیوتر | کارشناسان و تکنسین‌های مهندسی صنایع | مهندسان صنایع | مهندسان تولید و ساخت | کارشناسان و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | مهندسان سامانه‌های میکرو / میکروسیستم‌ها | دیسپچرها و توزیع‌کنندگان شبکه برق | تکنسین‌های رباتیک | مهندسان سیستم‌های انرژی خورشیدی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | سخن گفتن | شنیدن فعال | نگارش | ریاضیات | نظارت | یادگیری فعال | استراتژی‌های یادگیری | علوم پایه</t>
+          <t>درک مطلب | تفکر انتقادی | سخن گفتن | گوش دادن فعال | نگارش | ریاضیات | نظارت | یادگیری فعال | راهبردهای یادگیری | علوم</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | رایانه و الکترونیک | طراحی | ریاضیات | زبان انگلیسی | مکانیک | فیزیک | آموزش و تدریس</t>
+          <t>مهندسی و فناوری | رایانه و الکترونیک | طراحی | ریاضیات | زبان انگلیسی | مکانیک | فیزیک | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>بیان شفاهی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | دید نزدیک | درک شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال ریاضی | روانی ایده‌ها | انعطاف‌پذیری در طبقه‌بندی | اصالت و ابتکار | تجسم فضایی | محاسبات عددی | تشخیص گفتار | انعطاف‌پذیری نتیجه‌گیری | وضوح گفتار | چابکی انگشتان | پایداری دست و بازو | سرعت ادراک | توانایی تفکیک الگوها</t>
+          <t>بیان شفاهی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | بینایی نزدیک | درک شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال ریاضی | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | اصالت | تجسم | توانایی عددی | تشخیص گفتار | انعطاف‌پذیری بستار | وضوح گفتار | مهارت انگشتان | ثبات دست و بازو | سرعت ادراکی | سرعت بستار</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و کارشناسان فناوری مهندسی و عملیات هوافضا | تکنسین‌ها و کارشناسان فناوری کالیبراسیون | مهندسان سخت‌افزار کامپیوتر | مهندسان برق | تکنسین‌ها و کارشناسان فناوری مهندسی برق و الکترونیک | مونتاژکاران تجهیزات برق و الکترونیک | نقشه‌کش‌های برق و الکترونیک | تعمیرکاران تجهیزات تجاری و صنعتی برق و الکترونیک | تعمیرکاران برق و الکترونیک نیروگاه، پست برق و رله | تکنسین‌ها و کارشناسان فناوری الکترومکانیک و مکاترونیک | مونتاژکاران تجهیزات الکترومکانیکی | مهندسان صنایع | تکنسین‌ها و کارشناسان فناوری مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | مهندسان میکروسیستم‌ها | مهندسان فوتونیک | متخصصان سامانه‌های شناسایی با امواج رادیویی | مهندسان رباتیک | تکنسین‌های رباتیک</t>
+          <t>کارشناسان و تکنسین‌های مهندسی و عملیات هوافضا | تکنسین‌ها و کارشناسان فنی کالیبراسیون | مهندسان سخت‌افزار رایانه | مهندسان برق | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | نقشه‌کشان برق و الکترونیک | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | تعمیرکار تجهیزات الکتریکی نیروگاه، پست برق و رله | کارشناسان و تکنسین‌های الکترومکانیک و مکاترونیک | مونتاژکاران تجهیزات الکترومکانیکی | مهندسان صنایع | کارشناسان و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | مهندسان سامانه‌های میکرو / میکروسیستم‌ها | مهندسان فوتونیک | متخصصان سامانه‌های شناسایی با امواج رادیویی | مهندسان رباتیک | تکنسین‌های رباتیک</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | سخن گفتن | درک مطلب | نگارش | یادگیری فعال | نظارت</t>
+          <t>تفکر انتقادی | گوش دادن فعال | سخن گفتن | درک مطلب | نگارش | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | مهندسی و فناوری | زبان انگلیسی | طراحی | خدمات مشتریان و خدمات فردی | آموزش و تدریس | ریاضیات | مدیریت و امور اداری | مخابرات | تولید و فرآوری | فروش و بازاریابی</t>
+          <t>رایانه و الکترونیک | مهندسی و فناوری | زبان انگلیسی | طراحی | خدمات مشتری و شخصی | آموزش و پرورش | ریاضیات | مدیریت و اداره | مخابرات | تولید و فرآوری | فروش و بازاریابی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>استدلال قیاسی | درک شفاهی | حساسیت به مسئله | درک کتبی | استدلال استقرایی | مرتب‌سازی اطلاعات | دید نزدیک | بیان شفاهی | تشخیص گفتار | وضوح گفتار | بیان کتبی | روانی ایده‌ها | انعطاف‌پذیری در طبقه‌بندی | اصالت و ابتکار</t>
+          <t>استدلال قیاسی | درک شفاهی | حساسیت به مسئله | درک کتبی | استدلال استقرایی | ترتیب‌دهی اطلاعات | بینایی نزدیک | بیان شفاهی | تشخیص گفتار | وضوح گفتار | بیان کتبی | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | اصالت</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و کارشناسان فناوری مهندسی و عملیات هوافضا | تکنسین‌های پخش صدا و تصویر | تکنسین‌ها و کارشناسان فناوری کالیبراسیون | مهندسان سخت‌افزار کامپیوتر | معماران شبکه‌های کامپیوتری | مهندسان و معماران سیستم‌های کامپیوتری | مهندسان برق | تکنسین‌ها و کارشناسان فناوری مهندسی برق و الکترونیک | تعمیرکاران تجهیزات تجاری و صنعتی برق و الکترونیک | تکنسین‌ها و کارشناسان فناوری الکترومکانیک و مکاترونیک | مهندسان الکترونیک، به‌جز کامپیوتر | مهندسان مکاترونیک | مهندسان میکروسیستم‌ها | مهندسان فوتونیک | تکنسین‌های فوتونیک | نصابان و تعمیرکاران تجهیزات رادیویی، سلولی و دکل‌های مخابراتی | مهندسان رباتیک | تکنسین‌های رباتیک | توسعه‌دهندگان نرم‌افزار | متخصصان مهندسی مخابرات</t>
+          <t>کارشناسان و تکنسین‌های مهندسی و عملیات هوافضا | تکنسین‌های پخش و اتاق فرمان | تکنسین‌ها و کارشناسان فنی کالیبراسیون | مهندسان سخت‌افزار رایانه | معماران شبکه رایانه‌ای | مهندسان و معماران سامانه‌های رایانه‌ای | مهندسان برق | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | کارشناسان و تکنسین‌های الکترومکانیک و مکاترونیک | مهندسان الکترونیک، به‌جز کامپیوتر | مهندسان مکاترونیک | مهندسان سامانه‌های میکرو / میکروسیستم‌ها | مهندسان فوتونیک | تکنسین‌های فوتونیک و اپتیک | نصابان و تعمیرکاران تجهیزات رادیویی، سلولار و دکل‌های مخابراتی | مهندسان رباتیک | تکنسین‌های رباتیک | توسعه‌دهندگان نرم‌افزار | متخصصان مهندسی مخابرات</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>شنیدن فعال | نظارت | تفکر انتقادی | سخن گفتن | نگارش | درک مطلب | یادگیری فعال | ریاضیات | علوم پایه | استراتژی‌های یادگیری</t>
+          <t>گوش دادن فعال | نظارت | تفکر انتقادی | سخن گفتن | نگارش | درک مطلب | یادگیری فعال | ریاضیات | علوم | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | طراحی | شیمی | ریاضیات | ساختمان و سازه | زبان انگلیسی | فیزیک | خدمات مشتریان و خدمات فردی | زیست‌شناسی | رایانه و الکترونیک | حقوق و امور دولتی | مکانیک | مدیریت و امور اداری | اقتصاد و حسابداری | ایمنی و امنیت عمومی | آموزش و تدریس</t>
+          <t>مهندسی و فناوری | طراحی | شیمی | ریاضیات | ساختمان و ساخت‌وساز | زبان انگلیسی | فیزیک | خدمات مشتری و شخصی | زیست‌شناسی | رایانه و الکترونیک | قانون و دولت | مکانیک | مدیریت و اداره | اقتصاد و حسابداری | ایمنی و امنیت عمومی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | روانی ایده‌ها | مرتب‌سازی اطلاعات | دید نزدیک | تشخیص گفتار | وضوح گفتار | اصالت و ابتکار | محاسبات عددی | انعطاف‌پذیری نتیجه‌گیری | استدلال ریاضی | انعطاف‌پذیری در طبقه‌بندی | توجه انتخابی | تجسم فضایی | سرعت ادراک | حفظ و به‌خاطرسپاری</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | روانی ایده‌ها | ترتیب‌دهی اطلاعات | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | اصالت | توانایی عددی | انعطاف‌پذیری بستار | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | تجسم | سرعت ادراکی | حفظ کردن</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>مهندسان کشاورزی | متخصصان بهسازی اراضی و مدیران سایت | مهندسان شیمی | مهندسان عمران | دانشمندان حفاظت از منابع طبیعی | بازرسان انطباق زیست‌محیطی | تکنسین‌ها و کارشناسان فناوری مهندسی محیط‌زیست | برنامه‌ریزان احیای محیط‌زیست | تکنسین‌های علوم و حفاظت محیط‌زیست، شامل بهداشت | دانشمندان و متخصصان محیط‌زیست، شامل بهداشت | مهندسان بهداشت و ایمنی، به‌جز مهندسان و بازرسان ایمنی معدن | تکنسین‌های هیدرولوژی | هیدرولوژیست‌ها | بوم‌شناسان صنعتی | مهندسان هسته‌ای | متخصصان بهداشت و ایمنی حرفه‌ای | مهندسان نفت | متخصصان منابع آب | اپراتورهای تصفیه‌خانه و سیستم‌های آب و فاضلاب | مهندسان آب و فاضلاب</t>
+          <t>مهندسان کشاورزی | مدیران و کارشناسان احیا و بازسازی اراضی قهوه‌ای و آلوده | مهندسان شیمی | مهندسان عمران | دانشمندان حفاظت از منابع طبیعی | بازرسان رعایت ضوابط زیست‌محیطی | کارشناسان و تکنسین‌های مهندسی محیط زیست | برنامه‌ریزان احیای محیط زیست | تکنسین‌های علوم و بهداشت محیط زیست | کارشناسان و متخصصان علوم محیطی (شامل بهداشت) | مهندسان بهداشت و ایمنی، به‌جز مهندسان و بازرسان ایمنی معدن | تکنسین‌های آب‌شناسی و هیدرولوژی | آب‌شناسان و هیدرولوژیست‌ها | بوم‌شناسان صنعتی | مهندسان هسته‌ای | کارشناسان بهداشت حرفه‌ای و ایمنی کار | مهندسان نفت | کارشناسان و متخصصان مدیریت منابع آب | اپراتورهای تصفیه‌خانه و شبکه‌های انتقال آب و فاضلاب | مهندسان آب و فاضلاب</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | نگارش | تفکر انتقادی | سخن گفتن | نظارت | استراتژی‌های یادگیری | یادگیری فعال</t>
+          <t>درک مطلب | گوش دادن فعال | نگارش | تفکر انتقادی | سخن گفتن | نظارت | راهبردهای یادگیری | یادگیری فعال</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | مهندسی و فناوری | مدیریت و امور اداری | ایمنی و امنیت عمومی | خدمات مشتریان و خدمات فردی | حقوق و امور دولتی | آموزش و تدریس | مکانیک | ریاضیات | شیمی | طراحی | تولید و فرآوری | امور دفتری و اداری | فیزیک | ساختمان و سازه | روان‌شناسی | امور کارکنان و منابع انسانی | رایانه و الکترونیک</t>
+          <t>زبان انگلیسی | مهندسی و فناوری | مدیریت و اداره | ایمنی و امنیت عمومی | خدمات مشتری و شخصی | قانون و دولت | آموزش و پرورش | مکانیک | ریاضیات | شیمی | طراحی | تولید و فرآوری | اداری | فیزیک | ساختمان و ساخت‌وساز | روان‌شناسی | پرسنل و منابع انسانی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>استدلال استقرایی | استدلال قیاسی | درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | بیان کتبی | وضوح گفتار | انعطاف‌پذیری در طبقه‌بندی | روانی ایده‌ها | تشخیص گفتار | دید نزدیک | مرتب‌سازی اطلاعات | اصالت و ابتکار | دید دور | انعطاف‌پذیری نتیجه‌گیری | توجه انتخابی | سرعت ادراک | تشخیص رنگ‌ها</t>
+          <t>استدلال استقرایی | استدلال قیاسی | درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | بیان کتبی | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | تشخیص گفتار | بینایی نزدیک | ترتیب‌دهی اطلاعات | اصالت | بینایی دور | انعطاف‌پذیری بستار | توجه انتخابی | سرعت ادراکی | تشخیص رنگ بصری</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>بازرسان کشاورزی | بازرسان هوانوردی | مدیران انطباق و رعایت قوانین | بازرسان ساختمان و سازه | بازرسان انطباق زیست‌محیطی | تکنسین‌ها و کارشناسان فناوری مهندسی محیط‌زیست | مهندسان محیط‌زیست | تکنسین‌های علوم و حفاظت محیط‌زیست، شامل بهداشت | دانشمندان و متخصصان محیط‌زیست، شامل بهداشت | مهندسان پیشگیری و حفاظت از حریق | مهندسان عوامل انسانی و ارگونومی | تکنسین‌ها و کارشناسان فناوری مهندسی صنایع | مهندسان صنایع | متخصصان بهداشت و ایمنی حرفه‌ای | تکنسین‌های بهداشت و ایمنی حرفه‌ای | کارشناسان آزمون نفوذپذیری | مدیران سیستم‌های کنترل کیفیت | متخصصان مدیریت امنیت | بازرسان وسایل نقلیه، تجهیزات و سیستم‌های حمل‌ونقل، به‌جز هوانوردی | مهندسان اعتبارسنجی و صحه‌گذاری</t>
+          <t>بازرسان محصولات و فرآورده‌های کشاورزی | بازرسان هوانوردی و فرودگاهی | مدیران تطبیق و نظارت مقرراتی | بازرسان ساخت‌وساز و ساختمان | بازرسان رعایت ضوابط زیست‌محیطی | کارشناسان و تکنسین‌های مهندسی محیط زیست | مهندسان محیط‌زیست | تکنسین‌های علوم و بهداشت محیط زیست | کارشناسان و متخصصان علوم محیطی (شامل بهداشت) | مهندسان پیشگیری و حفاظت از حریق | مهندسان عوامل انسانی و ارگونومی | کارشناسان و تکنسین‌های مهندسی صنایع | مهندسان صنایع | کارشناسان بهداشت حرفه‌ای و ایمنی کار | کاردان‌ها و تکنسین‌های بهداشت حرفه‌ای و ایمنی کار | متخصصان آزمون نفوذپذیری و ارزیابی امنیتی | مدیران سیستم‌های کنترل کیفیت | کارشناسان مدیریت حراست و امنیت فیزیکی | بازرسان سامانه‌ها، تجهیزات و وسایل نقلیه ترابری (به‌جز هوانوردی) | مهندسان اعتبارسنجی و صحه‌گذاری</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | درک مطلب | شنیدن فعال | نگارش | یادگیری فعال | علوم پایه | ریاضیات | استراتژی‌های یادگیری | نظارت</t>
+          <t>تفکر انتقادی | سخن گفتن | درک مطلب | گوش دادن فعال | نگارش | یادگیری فعال | علوم | ریاضیات | راهبردهای یادگیری | نظارت</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | ساختمان و سازه | طراحی | ایمنی و امنیت عمومی | ریاضیات | زبان انگلیسی | فیزیک | شیمی | خدمات مشتریان و خدمات فردی | مکانیک | حقوق و امور دولتی | رایانه و الکترونیک | آموزش و تدریس | مدیریت و امور اداری</t>
+          <t>مهندسی و فناوری | ساختمان و ساخت‌وساز | طراحی | ایمنی و امنیت عمومی | ریاضیات | زبان انگلیسی | فیزیک | شیمی | خدمات مشتری و شخصی | مکانیک | قانون و دولت | رایانه و الکترونیک | آموزش و پرورش | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | دید نزدیک | درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | وضوح گفتار | مرتب‌سازی اطلاعات | انعطاف‌پذیری در طبقه‌بندی | انعطاف‌پذیری نتیجه‌گیری | تشخیص گفتار | روانی ایده‌ها | دید دور | تجسم فضایی | اصالت و ابتکار | استدلال ریاضی | سرعت ادراک | محاسبات عددی | تشخیص رنگ‌ها | توانایی تفکیک الگوها</t>
+          <t>حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | وضوح گفتار | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | تشخیص گفتار | روانی ایده‌ها | بینایی دور | تجسم | اصالت | استدلال ریاضی | سرعت ادراکی | توانایی عددی | تشخیص رنگ بصری | سرعت بستار</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و کارشناسان فناوری مهندسی عمران | مهندسان عمران | بازرسان ساختمان و سازه | مدیران مدیریت بحران و شرایط اضطراری | بازرسان انطباق زیست‌محیطی | تکنسین‌ها و کارشناسان فناوری مهندسی محیط‌زیست | مهندسان محیط‌زیست | بازرسان و کارشناسان بررسی حریق | آتش‌نشانان | سرپرستان رده‌اول کارکنان آتش‌نشانی و پیشگیری از حریق | بازرسان و متخصصان پیشگیری از حریق جنگل‌ها | بازرسان و کارشناسان اموال دولتی | مهندسان بهداشت و ایمنی، به‌جز مهندسان و بازرسان ایمنی معدن | مهندسان هسته‌ای | متخصصان بهداشت و ایمنی حرفه‌ای | تکنسین‌های بهداشت و ایمنی حرفه‌ای | کارشناسان آزمون نفوذپذیری | متخصصان مدیریت امنیت | نصابان سامانه‌های اعلام و اطفای حریق و دزدگیر | مهندسان آب و فاضلاب</t>
+          <t>کارشناسان و تکنسین‌های مهندسی عمران | مهندسان عمران | بازرسان ساخت‌وساز و ساختمان | مدیران مدیریت بحران و پدافند غیرعامل | بازرسان رعایت ضوابط زیست‌محیطی | کارشناسان و تکنسین‌های مهندسی محیط زیست | مهندسان محیط‌زیست | بازرسان و کارشناسان بررسی علل حریق | آتش‌نشانان | سرپرستان رده‌اول آتش‌نشانی و خدمات ایمنی و پیشگیری | بازرسان و کارشناسان پیشگیری از حریق جنگل | بازرسان و ممیزان اموال دولتی | مهندسان بهداشت و ایمنی، به‌جز مهندسان و بازرسان ایمنی معدن | مهندسان هسته‌ای | کارشناسان بهداشت حرفه‌ای و ایمنی کار | کاردان‌ها و تکنسین‌های بهداشت حرفه‌ای و ایمنی کار | متخصصان آزمون نفوذپذیری و ارزیابی امنیتی | کارشناسان مدیریت حراست و امنیت فیزیکی | نصاب سیستم‌های اعلام سرقت و حریق | مهندسان آب و فاضلاب</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | درک مطلب | سخن گفتن | نگارش | نظارت | ریاضیات | یادگیری فعال</t>
+          <t>تفکر انتقادی | گوش دادن فعال | درک مطلب | سخن گفتن | نگارش | نظارت | ریاضیات | یادگیری فعال</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | تولید و فرآوری | مکانیک | طراحی | زبان انگلیسی | ریاضیات | رایانه و الکترونیک | مدیریت و امور اداری | خدمات مشتریان و خدمات فردی | آموزش و تدریس | ایمنی و امنیت عمومی | فیزیک | امور دفتری و اداری</t>
+          <t>مهندسی و فناوری | تولید و فرآوری | مکانیک | طراحی | زبان انگلیسی | ریاضیات | رایانه و الکترونیک | مدیریت و اداره | خدمات مشتری و شخصی | آموزش و پرورش | ایمنی و امنیت عمومی | فیزیک | اداری</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | درک شفاهی | درک کتبی | حساسیت به مسئله | دید نزدیک | مرتب‌سازی اطلاعات | توجه انتخابی | انعطاف‌پذیری در طبقه‌بندی | روانی ایده‌ها | اصالت و ابتکار | تشخیص گفتار | وضوح گفتار | تجسم فضایی | محاسبات عددی | استدلال ریاضی | انعطاف‌پذیری نتیجه‌گیری | دید دور</t>
+          <t>بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | درک شفاهی | درک کتبی | حساسیت به مسئله | بینایی نزدیک | ترتیب‌دهی اطلاعات | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | تشخیص گفتار | وضوح گفتار | تجسم | توانایی عددی | استدلال ریاضی | انعطاف‌پذیری بستار | بینایی دور</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و کارشناسان فناوری مهندسی و عملیات هوافضا | مدیران معماری و مهندسی | مهندسان خودرو | تکنسین‌ها و کارشناسان فناوری کالیبراسیون | مهندسان برق | تکنسین‌ها و کارشناسان فناوری مهندسی برق و الکترونیک | مهندسان الکترونیک، به‌جز کامپیوتر | مهندسان عوامل انسانی و ارگونومی | تکنسین‌ها و کارشناسان فناوری مهندسی صنایع | مدیران تولید صنعتی | مهندسان لجستیک | مهندسان تولید و ساخت | مهندسان مواد | تکنسین‌ها و کارشناسان فناوری مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | متخصصان مدیریت پروژه | مدیران سیستم‌های کنترل کیفیت | مونتاژکاران گروهی | مهندسان اعتبارسنجی و صحه‌گذاری</t>
+          <t>کارشناسان و تکنسین‌های مهندسی و عملیات هوافضا | مدیران فنی و مهندسی و معماری | مهندسان خودرو | تکنسین‌ها و کارشناسان فنی کالیبراسیون | مهندسان برق | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | مهندسان الکترونیک، به‌جز کامپیوتر | مهندسان عوامل انسانی و ارگونومی | کارشناسان و تکنسین‌های مهندسی صنایع | مدیران تولید صنعتی | مهندسان لجستیک و زنجیره تأمین | مهندسان تولید و ساخت | مهندسان متالورژی و مواد | کارشناسان و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | کارشناسان مدیریت پروژه | مدیران سیستم‌های کنترل کیفیت | مونتاژکاران گروهی | مهندسان اعتبارسنجی و صحه‌گذاری</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | نگارش | شنیدن فعال | درک مطلب | یادگیری فعال | نظارت | ریاضیات | استراتژی‌های یادگیری | علوم پایه</t>
+          <t>تفکر انتقادی | سخن گفتن | نگارش | گوش دادن فعال | درک مطلب | یادگیری فعال | نظارت | ریاضیات | راهبردهای یادگیری | علوم</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>روان‌شناسی | زبان انگلیسی | طراحی | مهندسی و فناوری | آموزش و تدریس | ریاضیات | خدمات مشتریان و خدمات فردی | جامعه‌شناسی و انسان‌شناسی | تولید و فرآوری | رایانه و الکترونیک | مدیریت و امور اداری</t>
+          <t>روان‌شناسی | زبان انگلیسی | طراحی | مهندسی و فناوری | آموزش و پرورش | ریاضیات | خدمات مشتری و شخصی | جامعه‌شناسی و انسان‌شناسی | تولید و فرآوری | رایانه و الکترونیک | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | مرتب‌سازی اطلاعات | روانی ایده‌ها | انعطاف‌پذیری در طبقه‌بندی | اصالت و ابتکار | وضوح گفتار | استدلال ریاضی | دید نزدیک | تشخیص گفتار | محاسبات عددی | تجسم فضایی | دید دور | سرعت ادراک | انعطاف‌پذیری نتیجه‌گیری | توانایی تفکیک الگوها</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | اصالت | وضوح گفتار | استدلال ریاضی | بینایی نزدیک | تشخیص گفتار | توانایی عددی | تجسم | بینایی دور | سرعت ادراکی | انعطاف‌پذیری بستار | سرعت بستار</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مهندسان زیستی و پزشکی | مدیران داده‌های بالینی | دانشمندان پژوهش‌های کامپیوتر و اطلاعات | دانشمندان داده | تکنسین‌ها و کارشناسان فناوری مهندسی برق و الکترونیک | متخصصان انفورماتیک سلامت | مهندسان بهداشت و ایمنی، به‌جز مهندسان و بازرسان ایمنی معدن | تکنسین‌ها و کارشناسان فناوری مهندسی صنایع | مهندسان صنایع | مهندسان تولید و ساخت | تکنسین‌ها و کارشناسان فناوری مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | تکنسین‌ها و کارشناسان فناوری مهندسی نانوتکنولوژی | متخصصان بهداشت و ایمنی حرفه‌ای | تکنسین‌های بهداشت و ایمنی حرفه‌ای | کارشناسان آزمون نفوذپذیری | مهندسان رباتیک | تحلیل‌گران و آزمون‌گران تضمین کیفیت نرم‌افزار | مهندسان اعتبارسنجی و صحه‌گذاری</t>
+          <t>مهندسان پزشکی و بیوانجینیرینگ | مدیران داده‌های بالینی | پژوهشگران علوم رایانه و اطلاعات | دانشمندان داده | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | متخصصان انفورماتیک سلامت | مهندسان بهداشت و ایمنی، به‌جز مهندسان و بازرسان ایمنی معدن | کارشناسان و تکنسین‌های مهندسی صنایع | مهندسان صنایع | مهندسان تولید و ساخت | کارشناسان و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | کارشناسان و تکنسین‌های مهندسی نانوتکنولوژی | کارشناسان بهداشت حرفه‌ای و ایمنی کار | کاردان‌ها و تکنسین‌های بهداشت حرفه‌ای و ایمنی کار | متخصصان آزمون نفوذپذیری و ارزیابی امنیتی | مهندسان رباتیک | تحلیل‌گران و آزمون‌گران تضمین کیفیت نرم‌افزار | مهندسان اعتبارسنجی و صحه‌گذاری</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>درک مطلب | سخن گفتن | تفکر انتقادی | نگارش | شنیدن فعال | نظارت | علوم پایه | یادگیری فعال | ریاضیات | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | سخن گفتن | تفکر انتقادی | نگارش | گوش دادن فعال | نظارت | علوم | یادگیری فعال | ریاضیات | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | تولید و فرآوری | زبان انگلیسی | خدمات مشتریان و خدمات فردی | ریاضیات | طراحی | مکانیک | آموزش و تدریس | رایانه و الکترونیک | مدیریت و امور اداری</t>
+          <t>مهندسی و فناوری | تولید و فرآوری | زبان انگلیسی | خدمات مشتری و شخصی | ریاضیات | طراحی | مکانیک | آموزش و پرورش | رایانه و الکترونیک | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک کتبی | بیان کتبی | استدلال قیاسی | درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال استقرایی | دید نزدیک | وضوح گفتار | انعطاف‌پذیری در طبقه‌بندی | مرتب‌سازی اطلاعات | تشخیص گفتار | استدلال ریاضی | روانی ایده‌ها | محاسبات عددی | سرعت ادراک | انعطاف‌پذیری نتیجه‌گیری | توجه انتخابی | اصالت و ابتکار</t>
+          <t>درک کتبی | بیان کتبی | استدلال قیاسی | درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال استقرایی | بینایی نزدیک | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | تشخیص گفتار | استدلال ریاضی | روانی ایده‌ها | توانایی عددی | سرعت ادراکی | انعطاف‌پذیری بستار | توجه انتخابی | اصالت</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و کارشناسان فناوری مهندسی و عملیات هوافضا | تکنسین‌های مهندسی خودرو | مهندسان خودرو | تکنسین‌ها و کارشناسان فناوری کالیبراسیون | مهندسان برق | تکنسین‌ها و کارشناسان فناوری مهندسی برق و الکترونیک | تعمیرکاران تجهیزات تجاری و صنعتی برق و الکترونیک | مهندسان الکترونیک، به‌جز کامپیوتر | مهندسان عوامل انسانی و ارگونومی | تکنسین‌ها و کارشناسان فناوری مهندسی صنایع | مهندسان صنایع | مهندسان تولید و ساخت | تکنسین‌ها و کارشناسان فناوری مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | کارشناسان آزمون نفوذپذیری | تحلیل‌گران کنترل کیفیت | مدیران سیستم‌های کنترل کیفیت | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و آزمون‌گران تضمین کیفیت نرم‌افزار</t>
+          <t>کارشناسان و تکنسین‌های مهندسی و عملیات هوافضا | تکنسین‌های مهندسی خودرو | مهندسان خودرو | تکنسین‌ها و کارشناسان فنی کالیبراسیون | مهندسان برق | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | مهندسان الکترونیک، به‌جز کامپیوتر | مهندسان عوامل انسانی و ارگونومی | کارشناسان و تکنسین‌های مهندسی صنایع | مهندسان صنایع | مهندسان تولید و ساخت | کارشناسان و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | متخصصان آزمون نفوذپذیری و ارزیابی امنیتی | کارشناسان تحلیل کنترل کیفیت | مدیران سیستم‌های کنترل کیفیت | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و آزمون‌گران تضمین کیفیت نرم‌افزار</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ریاضیات | درک مطلب | سخن گفتن | نظارت | شنیدن فعال | نگارش | تفکر انتقادی | یادگیری فعال | استراتژی‌های یادگیری | علوم پایه</t>
+          <t>ریاضیات | درک مطلب | سخن گفتن | نظارت | گوش دادن فعال | نگارش | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری | علوم</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | تولید و فرآوری | مکانیک | طراحی | ریاضیات | رایانه و الکترونیک | زبان انگلیسی | فیزیک | مدیریت و امور اداری | آموزش و تدریس</t>
+          <t>مهندسی و فناوری | تولید و فرآوری | مکانیک | طراحی | ریاضیات | رایانه و الکترونیک | زبان انگلیسی | فیزیک | مدیریت و اداره | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>انعطاف‌پذیری در طبقه‌بندی | تجسم فضایی | دید نزدیک | درک شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک کتبی | بیان شفاهی | مرتب‌سازی اطلاعات | استدلال ریاضی | محاسبات عددی | بیان کتبی | روانی ایده‌ها | اصالت و ابتکار | انعطاف‌پذیری نتیجه‌گیری | تشخیص گفتار | دید دور | وضوح گفتار | توجه انتخابی | سرعت ادراک | توانایی تفکیک الگوها</t>
+          <t>انعطاف‌پذیری دسته‌بندی | تجسم | بینایی نزدیک | درک شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک کتبی | بیان شفاهی | ترتیب‌دهی اطلاعات | استدلال ریاضی | توانایی عددی | بیان کتبی | روانی ایده‌ها | اصالت | انعطاف‌پذیری بستار | تشخیص گفتار | بینایی دور | وضوح گفتار | توجه انتخابی | سرعت ادراکی | سرعت بستار</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و کارشناسان فناوری مهندسی و عملیات هوافضا | مهندسان خودرو | مهندسان شیمی | مهندسان برق | تکنسین‌ها و کارشناسان فناوری مهندسی برق و الکترونیک | مهندسان الکترونیک، به‌جز کامپیوتر | مهندسان عوامل انسانی و ارگونومی | تکنسین‌ها و کارشناسان فناوری مهندسی صنایع | مهندسان صنایع | مدیران تولید صنعتی | مهندسان لجستیک | مهندسان مواد | دانشمندان علم مواد | تکنسین‌ها و کارشناسان فناوری مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | مهندسان میکروسیستم‌ها | تکنسین‌های رباتیک | مونتاژکاران گروهی | مهندسان اعتبارسنجی و صحه‌گذاری</t>
+          <t>کارشناسان و تکنسین‌های مهندسی و عملیات هوافضا | مهندسان خودرو | مهندسان شیمی | مهندسان برق | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | مهندسان الکترونیک، به‌جز کامپیوتر | مهندسان عوامل انسانی و ارگونومی | کارشناسان و تکنسین‌های مهندسی صنایع | مهندسان صنایع | مدیران تولید صنعتی | مهندسان لجستیک و زنجیره تأمین | مهندسان متالورژی و مواد | کارشناسان و دانشمندان علوم مواد | کارشناسان و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | مهندسان سامانه‌های میکرو / میکروسیستم‌ها | تکنسین‌های رباتیک | مونتاژکاران گروهی | مهندسان اعتبارسنجی و صحه‌گذاری</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
